--- a/files/holidays_ID.xlsx
+++ b/files/holidays_ID.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1222"/>
+  <dimension ref="A1:D1225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,11 @@
           <t>Libur</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -461,6 +466,7 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -474,6 +480,7 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -483,6 +490,7 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -492,6 +500,7 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -501,6 +510,7 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -510,6 +520,7 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -519,6 +530,7 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -532,6 +544,7 @@
       <c r="C9" t="n">
         <v>1</v>
       </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -545,6 +558,7 @@
       <c r="C10" t="n">
         <v>1</v>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -554,6 +568,7 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -563,6 +578,7 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -572,6 +588,7 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -581,6 +598,7 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -590,6 +608,7 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -603,6 +622,7 @@
       <c r="C16" t="n">
         <v>1</v>
       </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -616,6 +636,7 @@
       <c r="C17" t="n">
         <v>1</v>
       </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -625,6 +646,7 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -634,6 +656,7 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -643,6 +666,7 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -652,6 +676,7 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -661,6 +686,7 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -674,6 +700,7 @@
       <c r="C23" t="n">
         <v>1</v>
       </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -687,6 +714,7 @@
       <c r="C24" t="n">
         <v>1</v>
       </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -696,6 +724,7 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -705,6 +734,7 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -714,6 +744,7 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -723,6 +754,7 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -732,6 +764,7 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -745,6 +778,7 @@
       <c r="C30" t="n">
         <v>1</v>
       </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -758,6 +792,7 @@
       <c r="C31" t="n">
         <v>1</v>
       </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -767,6 +802,7 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -780,6 +816,7 @@
       <c r="C33" t="n">
         <v>1</v>
       </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -789,6 +826,7 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -798,6 +836,7 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -807,6 +846,7 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -820,6 +860,7 @@
       <c r="C37" t="n">
         <v>1</v>
       </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -833,6 +874,7 @@
       <c r="C38" t="n">
         <v>1</v>
       </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -842,6 +884,7 @@
       <c r="C39" t="n">
         <v>0</v>
       </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -851,6 +894,7 @@
       <c r="C40" t="n">
         <v>0</v>
       </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -860,6 +904,7 @@
       <c r="C41" t="n">
         <v>0</v>
       </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -869,6 +914,7 @@
       <c r="C42" t="n">
         <v>0</v>
       </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -878,6 +924,7 @@
       <c r="C43" t="n">
         <v>0</v>
       </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -891,6 +938,7 @@
       <c r="C44" t="n">
         <v>1</v>
       </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -904,6 +952,7 @@
       <c r="C45" t="n">
         <v>1</v>
       </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -913,6 +962,7 @@
       <c r="C46" t="n">
         <v>0</v>
       </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -922,6 +972,7 @@
       <c r="C47" t="n">
         <v>0</v>
       </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -931,6 +982,7 @@
       <c r="C48" t="n">
         <v>0</v>
       </c>
+      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -940,6 +992,7 @@
       <c r="C49" t="n">
         <v>0</v>
       </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -949,6 +1002,7 @@
       <c r="C50" t="n">
         <v>0</v>
       </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -962,6 +1016,7 @@
       <c r="C51" t="n">
         <v>1</v>
       </c>
+      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -975,6 +1030,7 @@
       <c r="C52" t="n">
         <v>1</v>
       </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -984,6 +1040,7 @@
       <c r="C53" t="n">
         <v>0</v>
       </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -993,6 +1050,7 @@
       <c r="C54" t="n">
         <v>0</v>
       </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -1002,6 +1060,7 @@
       <c r="C55" t="n">
         <v>0</v>
       </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -1011,6 +1070,7 @@
       <c r="C56" t="n">
         <v>0</v>
       </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -1020,6 +1080,7 @@
       <c r="C57" t="n">
         <v>0</v>
       </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -1033,6 +1094,7 @@
       <c r="C58" t="n">
         <v>1</v>
       </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -1046,6 +1108,7 @@
       <c r="C59" t="n">
         <v>1</v>
       </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -1059,6 +1122,7 @@
       <c r="C60" t="n">
         <v>1</v>
       </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -1068,6 +1132,7 @@
       <c r="C61" t="n">
         <v>0</v>
       </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -1077,6 +1142,7 @@
       <c r="C62" t="n">
         <v>0</v>
       </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -1090,6 +1156,7 @@
       <c r="C63" t="n">
         <v>1</v>
       </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -1099,6 +1166,7 @@
       <c r="C64" t="n">
         <v>0</v>
       </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -1112,6 +1180,7 @@
       <c r="C65" t="n">
         <v>1</v>
       </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -1125,6 +1194,7 @@
       <c r="C66" t="n">
         <v>1</v>
       </c>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -1134,6 +1204,7 @@
       <c r="C67" t="n">
         <v>0</v>
       </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -1143,6 +1214,7 @@
       <c r="C68" t="n">
         <v>0</v>
       </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -1152,6 +1224,7 @@
       <c r="C69" t="n">
         <v>0</v>
       </c>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -1161,6 +1234,7 @@
       <c r="C70" t="n">
         <v>0</v>
       </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -1170,6 +1244,7 @@
       <c r="C71" t="n">
         <v>0</v>
       </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -1183,6 +1258,7 @@
       <c r="C72" t="n">
         <v>1</v>
       </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -1196,6 +1272,7 @@
       <c r="C73" t="n">
         <v>1</v>
       </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -1205,6 +1282,7 @@
       <c r="C74" t="n">
         <v>0</v>
       </c>
+      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -1214,6 +1292,7 @@
       <c r="C75" t="n">
         <v>0</v>
       </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -1223,6 +1302,7 @@
       <c r="C76" t="n">
         <v>0</v>
       </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -1232,6 +1312,7 @@
       <c r="C77" t="n">
         <v>0</v>
       </c>
+      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -1241,6 +1322,7 @@
       <c r="C78" t="n">
         <v>0</v>
       </c>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -1254,6 +1336,7 @@
       <c r="C79" t="n">
         <v>1</v>
       </c>
+      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -1267,6 +1350,7 @@
       <c r="C80" t="n">
         <v>1</v>
       </c>
+      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -1276,6 +1360,7 @@
       <c r="C81" t="n">
         <v>0</v>
       </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -1285,6 +1370,7 @@
       <c r="C82" t="n">
         <v>0</v>
       </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -1294,6 +1380,7 @@
       <c r="C83" t="n">
         <v>0</v>
       </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -1303,6 +1390,7 @@
       <c r="C84" t="n">
         <v>0</v>
       </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -1312,6 +1400,7 @@
       <c r="C85" t="n">
         <v>0</v>
       </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -1325,6 +1414,7 @@
       <c r="C86" t="n">
         <v>1</v>
       </c>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -1338,6 +1428,7 @@
       <c r="C87" t="n">
         <v>1</v>
       </c>
+      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -1347,6 +1438,7 @@
       <c r="C88" t="n">
         <v>0</v>
       </c>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -1356,6 +1448,7 @@
       <c r="C89" t="n">
         <v>0</v>
       </c>
+      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -1365,6 +1458,7 @@
       <c r="C90" t="n">
         <v>0</v>
       </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -1374,6 +1468,7 @@
       <c r="C91" t="n">
         <v>0</v>
       </c>
+      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -1383,6 +1478,7 @@
       <c r="C92" t="n">
         <v>0</v>
       </c>
+      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -1396,6 +1492,7 @@
       <c r="C93" t="n">
         <v>1</v>
       </c>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -1409,6 +1506,7 @@
       <c r="C94" t="n">
         <v>1</v>
       </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -1418,6 +1516,7 @@
       <c r="C95" t="n">
         <v>0</v>
       </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -1427,6 +1526,7 @@
       <c r="C96" t="n">
         <v>0</v>
       </c>
+      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -1436,6 +1536,7 @@
       <c r="C97" t="n">
         <v>0</v>
       </c>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -1445,6 +1546,7 @@
       <c r="C98" t="n">
         <v>0</v>
       </c>
+      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -1454,6 +1556,7 @@
       <c r="C99" t="n">
         <v>0</v>
       </c>
+      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -1467,6 +1570,7 @@
       <c r="C100" t="n">
         <v>1</v>
       </c>
+      <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -1480,6 +1584,7 @@
       <c r="C101" t="n">
         <v>1</v>
       </c>
+      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -1489,6 +1594,7 @@
       <c r="C102" t="n">
         <v>0</v>
       </c>
+      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -1498,6 +1604,7 @@
       <c r="C103" t="n">
         <v>0</v>
       </c>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -1507,6 +1614,7 @@
       <c r="C104" t="n">
         <v>0</v>
       </c>
+      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -1516,6 +1624,7 @@
       <c r="C105" t="n">
         <v>0</v>
       </c>
+      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -1529,6 +1638,7 @@
       <c r="C106" t="n">
         <v>1</v>
       </c>
+      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -1542,6 +1652,7 @@
       <c r="C107" t="n">
         <v>1</v>
       </c>
+      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -1555,6 +1666,7 @@
       <c r="C108" t="n">
         <v>1</v>
       </c>
+      <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -1564,6 +1676,7 @@
       <c r="C109" t="n">
         <v>0</v>
       </c>
+      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -1573,6 +1686,7 @@
       <c r="C110" t="n">
         <v>0</v>
       </c>
+      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -1582,6 +1696,7 @@
       <c r="C111" t="n">
         <v>0</v>
       </c>
+      <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -1591,6 +1706,7 @@
       <c r="C112" t="n">
         <v>0</v>
       </c>
+      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -1600,6 +1716,7 @@
       <c r="C113" t="n">
         <v>0</v>
       </c>
+      <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -1613,6 +1730,7 @@
       <c r="C114" t="n">
         <v>1</v>
       </c>
+      <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -1626,6 +1744,7 @@
       <c r="C115" t="n">
         <v>1</v>
       </c>
+      <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -1635,6 +1754,7 @@
       <c r="C116" t="n">
         <v>0</v>
       </c>
+      <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -1644,6 +1764,7 @@
       <c r="C117" t="n">
         <v>0</v>
       </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -1653,6 +1774,7 @@
       <c r="C118" t="n">
         <v>0</v>
       </c>
+      <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -1662,6 +1784,7 @@
       <c r="C119" t="n">
         <v>0</v>
       </c>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -1671,6 +1794,7 @@
       <c r="C120" t="n">
         <v>0</v>
       </c>
+      <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -1684,6 +1808,7 @@
       <c r="C121" t="n">
         <v>1</v>
       </c>
+      <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -1697,6 +1822,7 @@
       <c r="C122" t="n">
         <v>1</v>
       </c>
+      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -1710,6 +1836,7 @@
       <c r="C123" t="n">
         <v>1</v>
       </c>
+      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -1723,6 +1850,7 @@
       <c r="C124" t="n">
         <v>1</v>
       </c>
+      <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -1736,6 +1864,7 @@
       <c r="C125" t="n">
         <v>1</v>
       </c>
+      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -1749,6 +1878,7 @@
       <c r="C126" t="n">
         <v>1</v>
       </c>
+      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -1762,6 +1892,7 @@
       <c r="C127" t="n">
         <v>1</v>
       </c>
+      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -1775,6 +1906,7 @@
       <c r="C128" t="n">
         <v>1</v>
       </c>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -1788,6 +1920,7 @@
       <c r="C129" t="n">
         <v>1</v>
       </c>
+      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -1797,6 +1930,7 @@
       <c r="C130" t="n">
         <v>0</v>
       </c>
+      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -1806,6 +1940,7 @@
       <c r="C131" t="n">
         <v>0</v>
       </c>
+      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -1815,6 +1950,7 @@
       <c r="C132" t="n">
         <v>0</v>
       </c>
+      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -1824,6 +1960,7 @@
       <c r="C133" t="n">
         <v>0</v>
       </c>
+      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -1833,6 +1970,7 @@
       <c r="C134" t="n">
         <v>0</v>
       </c>
+      <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -1846,6 +1984,7 @@
       <c r="C135" t="n">
         <v>1</v>
       </c>
+      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -1859,6 +1998,7 @@
       <c r="C136" t="n">
         <v>1</v>
       </c>
+      <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -1872,6 +2012,7 @@
       <c r="C137" t="n">
         <v>1</v>
       </c>
+      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -1881,6 +2022,7 @@
       <c r="C138" t="n">
         <v>0</v>
       </c>
+      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -1890,6 +2032,7 @@
       <c r="C139" t="n">
         <v>0</v>
       </c>
+      <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -1899,6 +2042,7 @@
       <c r="C140" t="n">
         <v>0</v>
       </c>
+      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -1908,6 +2052,7 @@
       <c r="C141" t="n">
         <v>0</v>
       </c>
+      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -1921,6 +2066,7 @@
       <c r="C142" t="n">
         <v>1</v>
       </c>
+      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -1934,6 +2080,7 @@
       <c r="C143" t="n">
         <v>1</v>
       </c>
+      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -1943,6 +2090,7 @@
       <c r="C144" t="n">
         <v>0</v>
       </c>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -1952,6 +2100,7 @@
       <c r="C145" t="n">
         <v>0</v>
       </c>
+      <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -1961,6 +2110,7 @@
       <c r="C146" t="n">
         <v>0</v>
       </c>
+      <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -1974,6 +2124,7 @@
       <c r="C147" t="n">
         <v>1</v>
       </c>
+      <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -1983,6 +2134,7 @@
       <c r="C148" t="n">
         <v>0</v>
       </c>
+      <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -1996,6 +2148,7 @@
       <c r="C149" t="n">
         <v>1</v>
       </c>
+      <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -2009,6 +2162,7 @@
       <c r="C150" t="n">
         <v>1</v>
       </c>
+      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -2018,6 +2172,7 @@
       <c r="C151" t="n">
         <v>0</v>
       </c>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -2027,6 +2182,7 @@
       <c r="C152" t="n">
         <v>0</v>
       </c>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -2040,6 +2196,7 @@
       <c r="C153" t="n">
         <v>1</v>
       </c>
+      <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -2049,6 +2206,7 @@
       <c r="C154" t="n">
         <v>0</v>
       </c>
+      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -2058,6 +2216,7 @@
       <c r="C155" t="n">
         <v>0</v>
       </c>
+      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -2071,6 +2230,7 @@
       <c r="C156" t="n">
         <v>1</v>
       </c>
+      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -2084,6 +2244,7 @@
       <c r="C157" t="n">
         <v>1</v>
       </c>
+      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -2093,6 +2254,7 @@
       <c r="C158" t="n">
         <v>0</v>
       </c>
+      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -2102,6 +2264,7 @@
       <c r="C159" t="n">
         <v>0</v>
       </c>
+      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -2111,6 +2274,7 @@
       <c r="C160" t="n">
         <v>0</v>
       </c>
+      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -2120,6 +2284,7 @@
       <c r="C161" t="n">
         <v>0</v>
       </c>
+      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -2129,6 +2294,7 @@
       <c r="C162" t="n">
         <v>0</v>
       </c>
+      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -2142,6 +2308,7 @@
       <c r="C163" t="n">
         <v>1</v>
       </c>
+      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -2155,6 +2322,7 @@
       <c r="C164" t="n">
         <v>1</v>
       </c>
+      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -2164,6 +2332,7 @@
       <c r="C165" t="n">
         <v>0</v>
       </c>
+      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -2173,6 +2342,7 @@
       <c r="C166" t="n">
         <v>0</v>
       </c>
+      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -2182,6 +2352,7 @@
       <c r="C167" t="n">
         <v>0</v>
       </c>
+      <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -2195,6 +2366,7 @@
       <c r="C168" t="n">
         <v>1</v>
       </c>
+      <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -2208,6 +2380,7 @@
       <c r="C169" t="n">
         <v>1</v>
       </c>
+      <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -2221,6 +2394,7 @@
       <c r="C170" t="n">
         <v>1</v>
       </c>
+      <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -2234,6 +2408,7 @@
       <c r="C171" t="n">
         <v>1</v>
       </c>
+      <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -2247,6 +2422,7 @@
       <c r="C172" t="n">
         <v>1</v>
       </c>
+      <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -2260,6 +2436,7 @@
       <c r="C173" t="n">
         <v>1</v>
       </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -2273,6 +2450,7 @@
       <c r="C174" t="n">
         <v>1</v>
       </c>
+      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -2286,6 +2464,7 @@
       <c r="C175" t="n">
         <v>1</v>
       </c>
+      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -2299,6 +2478,7 @@
       <c r="C176" t="n">
         <v>1</v>
       </c>
+      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -2312,6 +2492,7 @@
       <c r="C177" t="n">
         <v>1</v>
       </c>
+      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -2325,6 +2506,7 @@
       <c r="C178" t="n">
         <v>1</v>
       </c>
+      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -2338,6 +2520,7 @@
       <c r="C179" t="n">
         <v>1</v>
       </c>
+      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -2351,6 +2534,7 @@
       <c r="C180" t="n">
         <v>1</v>
       </c>
+      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -2364,6 +2548,7 @@
       <c r="C181" t="n">
         <v>1</v>
       </c>
+      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -2377,6 +2562,7 @@
       <c r="C182" t="n">
         <v>1</v>
       </c>
+      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -2390,6 +2576,7 @@
       <c r="C183" t="n">
         <v>1</v>
       </c>
+      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -2403,6 +2590,7 @@
       <c r="C184" t="n">
         <v>1</v>
       </c>
+      <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -2416,6 +2604,7 @@
       <c r="C185" t="n">
         <v>1</v>
       </c>
+      <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -2429,6 +2618,7 @@
       <c r="C186" t="n">
         <v>1</v>
       </c>
+      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -2442,6 +2632,7 @@
       <c r="C187" t="n">
         <v>1</v>
       </c>
+      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -2455,6 +2646,7 @@
       <c r="C188" t="n">
         <v>1</v>
       </c>
+      <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -2468,6 +2660,7 @@
       <c r="C189" t="n">
         <v>1</v>
       </c>
+      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -2481,6 +2674,7 @@
       <c r="C190" t="n">
         <v>1</v>
       </c>
+      <c r="D190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -2494,6 +2688,7 @@
       <c r="C191" t="n">
         <v>1</v>
       </c>
+      <c r="D191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -2507,6 +2702,7 @@
       <c r="C192" t="n">
         <v>1</v>
       </c>
+      <c r="D192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -2520,6 +2716,7 @@
       <c r="C193" t="n">
         <v>1</v>
       </c>
+      <c r="D193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -2533,6 +2730,7 @@
       <c r="C194" t="n">
         <v>1</v>
       </c>
+      <c r="D194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -2546,6 +2744,7 @@
       <c r="C195" t="n">
         <v>1</v>
       </c>
+      <c r="D195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -2559,6 +2758,7 @@
       <c r="C196" t="n">
         <v>1</v>
       </c>
+      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -2572,6 +2772,7 @@
       <c r="C197" t="n">
         <v>1</v>
       </c>
+      <c r="D197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -2585,6 +2786,7 @@
       <c r="C198" t="n">
         <v>1</v>
       </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -2598,6 +2800,7 @@
       <c r="C199" t="n">
         <v>1</v>
       </c>
+      <c r="D199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -2607,6 +2810,7 @@
       <c r="C200" t="n">
         <v>0</v>
       </c>
+      <c r="D200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -2616,6 +2820,7 @@
       <c r="C201" t="n">
         <v>0</v>
       </c>
+      <c r="D201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -2625,6 +2830,7 @@
       <c r="C202" t="n">
         <v>0</v>
       </c>
+      <c r="D202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
@@ -2634,6 +2840,7 @@
       <c r="C203" t="n">
         <v>0</v>
       </c>
+      <c r="D203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -2643,6 +2850,7 @@
       <c r="C204" t="n">
         <v>0</v>
       </c>
+      <c r="D204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
@@ -2656,6 +2864,7 @@
       <c r="C205" t="n">
         <v>1</v>
       </c>
+      <c r="D205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -2669,6 +2878,7 @@
       <c r="C206" t="n">
         <v>1</v>
       </c>
+      <c r="D206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
@@ -2678,6 +2888,7 @@
       <c r="C207" t="n">
         <v>0</v>
       </c>
+      <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
@@ -2687,6 +2898,7 @@
       <c r="C208" t="n">
         <v>0</v>
       </c>
+      <c r="D208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
@@ -2696,6 +2908,7 @@
       <c r="C209" t="n">
         <v>0</v>
       </c>
+      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
@@ -2705,6 +2918,7 @@
       <c r="C210" t="n">
         <v>0</v>
       </c>
+      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
@@ -2714,6 +2928,7 @@
       <c r="C211" t="n">
         <v>0</v>
       </c>
+      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
@@ -2727,6 +2942,7 @@
       <c r="C212" t="n">
         <v>1</v>
       </c>
+      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
@@ -2740,6 +2956,7 @@
       <c r="C213" t="n">
         <v>1</v>
       </c>
+      <c r="D213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -2749,6 +2966,7 @@
       <c r="C214" t="n">
         <v>0</v>
       </c>
+      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
@@ -2758,6 +2976,7 @@
       <c r="C215" t="n">
         <v>0</v>
       </c>
+      <c r="D215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -2767,6 +2986,7 @@
       <c r="C216" t="n">
         <v>0</v>
       </c>
+      <c r="D216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
@@ -2776,6 +2996,7 @@
       <c r="C217" t="n">
         <v>0</v>
       </c>
+      <c r="D217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -2785,6 +3006,7 @@
       <c r="C218" t="n">
         <v>0</v>
       </c>
+      <c r="D218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
@@ -2798,6 +3020,7 @@
       <c r="C219" t="n">
         <v>1</v>
       </c>
+      <c r="D219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
@@ -2811,6 +3034,7 @@
       <c r="C220" t="n">
         <v>1</v>
       </c>
+      <c r="D220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
@@ -2820,6 +3044,7 @@
       <c r="C221" t="n">
         <v>0</v>
       </c>
+      <c r="D221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
@@ -2829,6 +3054,7 @@
       <c r="C222" t="n">
         <v>0</v>
       </c>
+      <c r="D222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
@@ -2838,6 +3064,7 @@
       <c r="C223" t="n">
         <v>0</v>
       </c>
+      <c r="D223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -2847,6 +3074,7 @@
       <c r="C224" t="n">
         <v>0</v>
       </c>
+      <c r="D224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
@@ -2856,6 +3084,7 @@
       <c r="C225" t="n">
         <v>0</v>
       </c>
+      <c r="D225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -2869,6 +3098,7 @@
       <c r="C226" t="n">
         <v>1</v>
       </c>
+      <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
@@ -2882,6 +3112,7 @@
       <c r="C227" t="n">
         <v>1</v>
       </c>
+      <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -2891,6 +3122,7 @@
       <c r="C228" t="n">
         <v>0</v>
       </c>
+      <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
@@ -2900,6 +3132,7 @@
       <c r="C229" t="n">
         <v>0</v>
       </c>
+      <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -2913,6 +3146,7 @@
       <c r="C230" t="n">
         <v>1</v>
       </c>
+      <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
@@ -2922,6 +3156,7 @@
       <c r="C231" t="n">
         <v>0</v>
       </c>
+      <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -2931,6 +3166,7 @@
       <c r="C232" t="n">
         <v>0</v>
       </c>
+      <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
@@ -2944,6 +3180,7 @@
       <c r="C233" t="n">
         <v>1</v>
       </c>
+      <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -2957,6 +3194,7 @@
       <c r="C234" t="n">
         <v>1</v>
       </c>
+      <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
@@ -2966,6 +3204,7 @@
       <c r="C235" t="n">
         <v>0</v>
       </c>
+      <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -2975,6 +3214,7 @@
       <c r="C236" t="n">
         <v>0</v>
       </c>
+      <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
@@ -2984,6 +3224,7 @@
       <c r="C237" t="n">
         <v>0</v>
       </c>
+      <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -2993,6 +3234,7 @@
       <c r="C238" t="n">
         <v>0</v>
       </c>
+      <c r="D238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
@@ -3002,6 +3244,7 @@
       <c r="C239" t="n">
         <v>0</v>
       </c>
+      <c r="D239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -3015,6 +3258,7 @@
       <c r="C240" t="n">
         <v>1</v>
       </c>
+      <c r="D240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
@@ -3028,6 +3272,7 @@
       <c r="C241" t="n">
         <v>1</v>
       </c>
+      <c r="D241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
@@ -3037,6 +3282,7 @@
       <c r="C242" t="n">
         <v>0</v>
       </c>
+      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
@@ -3046,6 +3292,7 @@
       <c r="C243" t="n">
         <v>0</v>
       </c>
+      <c r="D243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -3055,6 +3302,7 @@
       <c r="C244" t="n">
         <v>0</v>
       </c>
+      <c r="D244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
@@ -3064,6 +3312,7 @@
       <c r="C245" t="n">
         <v>0</v>
       </c>
+      <c r="D245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
@@ -3073,6 +3322,7 @@
       <c r="C246" t="n">
         <v>0</v>
       </c>
+      <c r="D246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
@@ -3086,6 +3336,7 @@
       <c r="C247" t="n">
         <v>1</v>
       </c>
+      <c r="D247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -3099,6 +3350,7 @@
       <c r="C248" t="n">
         <v>1</v>
       </c>
+      <c r="D248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
@@ -3108,6 +3360,7 @@
       <c r="C249" t="n">
         <v>0</v>
       </c>
+      <c r="D249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -3117,6 +3370,7 @@
       <c r="C250" t="n">
         <v>0</v>
       </c>
+      <c r="D250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
@@ -3126,6 +3380,7 @@
       <c r="C251" t="n">
         <v>0</v>
       </c>
+      <c r="D251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
@@ -3135,6 +3390,7 @@
       <c r="C252" t="n">
         <v>0</v>
       </c>
+      <c r="D252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
@@ -3144,6 +3400,7 @@
       <c r="C253" t="n">
         <v>0</v>
       </c>
+      <c r="D253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -3157,6 +3414,7 @@
       <c r="C254" t="n">
         <v>1</v>
       </c>
+      <c r="D254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
@@ -3170,6 +3428,7 @@
       <c r="C255" t="n">
         <v>1</v>
       </c>
+      <c r="D255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -3179,6 +3438,7 @@
       <c r="C256" t="n">
         <v>0</v>
       </c>
+      <c r="D256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
@@ -3188,6 +3448,7 @@
       <c r="C257" t="n">
         <v>0</v>
       </c>
+      <c r="D257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -3197,6 +3458,7 @@
       <c r="C258" t="n">
         <v>0</v>
       </c>
+      <c r="D258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
@@ -3206,6 +3468,7 @@
       <c r="C259" t="n">
         <v>0</v>
       </c>
+      <c r="D259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -3215,6 +3478,7 @@
       <c r="C260" t="n">
         <v>0</v>
       </c>
+      <c r="D260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
@@ -3228,6 +3492,7 @@
       <c r="C261" t="n">
         <v>1</v>
       </c>
+      <c r="D261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -3241,6 +3506,7 @@
       <c r="C262" t="n">
         <v>1</v>
       </c>
+      <c r="D262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
@@ -3250,6 +3516,7 @@
       <c r="C263" t="n">
         <v>0</v>
       </c>
+      <c r="D263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -3259,6 +3526,7 @@
       <c r="C264" t="n">
         <v>0</v>
       </c>
+      <c r="D264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
@@ -3268,6 +3536,7 @@
       <c r="C265" t="n">
         <v>0</v>
       </c>
+      <c r="D265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -3277,6 +3546,7 @@
       <c r="C266" t="n">
         <v>0</v>
       </c>
+      <c r="D266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
@@ -3286,6 +3556,7 @@
       <c r="C267" t="n">
         <v>0</v>
       </c>
+      <c r="D267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
@@ -3299,6 +3570,7 @@
       <c r="C268" t="n">
         <v>1</v>
       </c>
+      <c r="D268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
@@ -3312,6 +3584,7 @@
       <c r="C269" t="n">
         <v>1</v>
       </c>
+      <c r="D269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -3321,6 +3594,7 @@
       <c r="C270" t="n">
         <v>0</v>
       </c>
+      <c r="D270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
@@ -3330,6 +3604,7 @@
       <c r="C271" t="n">
         <v>0</v>
       </c>
+      <c r="D271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -3339,6 +3614,7 @@
       <c r="C272" t="n">
         <v>0</v>
       </c>
+      <c r="D272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
@@ -3348,6 +3624,7 @@
       <c r="C273" t="n">
         <v>0</v>
       </c>
+      <c r="D273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -3357,6 +3634,7 @@
       <c r="C274" t="n">
         <v>0</v>
       </c>
+      <c r="D274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -3370,6 +3648,7 @@
       <c r="C275" t="n">
         <v>1</v>
       </c>
+      <c r="D275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -3383,6 +3662,7 @@
       <c r="C276" t="n">
         <v>1</v>
       </c>
+      <c r="D276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
@@ -3392,6 +3672,7 @@
       <c r="C277" t="n">
         <v>0</v>
       </c>
+      <c r="D277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -3401,6 +3682,7 @@
       <c r="C278" t="n">
         <v>0</v>
       </c>
+      <c r="D278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -3410,6 +3692,7 @@
       <c r="C279" t="n">
         <v>0</v>
       </c>
+      <c r="D279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
@@ -3419,6 +3702,7 @@
       <c r="C280" t="n">
         <v>0</v>
       </c>
+      <c r="D280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
@@ -3428,6 +3712,7 @@
       <c r="C281" t="n">
         <v>0</v>
       </c>
+      <c r="D281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -3441,6 +3726,7 @@
       <c r="C282" t="n">
         <v>1</v>
       </c>
+      <c r="D282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
@@ -3454,6 +3740,7 @@
       <c r="C283" t="n">
         <v>1</v>
       </c>
+      <c r="D283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -3463,6 +3750,7 @@
       <c r="C284" t="n">
         <v>0</v>
       </c>
+      <c r="D284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n">
@@ -3472,6 +3760,7 @@
       <c r="C285" t="n">
         <v>0</v>
       </c>
+      <c r="D285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
@@ -3481,6 +3770,7 @@
       <c r="C286" t="n">
         <v>0</v>
       </c>
+      <c r="D286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
@@ -3490,6 +3780,7 @@
       <c r="C287" t="n">
         <v>0</v>
       </c>
+      <c r="D287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -3499,6 +3790,7 @@
       <c r="C288" t="n">
         <v>0</v>
       </c>
+      <c r="D288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
@@ -3512,6 +3804,7 @@
       <c r="C289" t="n">
         <v>1</v>
       </c>
+      <c r="D289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
@@ -3525,6 +3818,7 @@
       <c r="C290" t="n">
         <v>1</v>
       </c>
+      <c r="D290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
@@ -3534,6 +3828,7 @@
       <c r="C291" t="n">
         <v>0</v>
       </c>
+      <c r="D291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
@@ -3543,6 +3838,7 @@
       <c r="C292" t="n">
         <v>0</v>
       </c>
+      <c r="D292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
@@ -3552,6 +3848,7 @@
       <c r="C293" t="n">
         <v>0</v>
       </c>
+      <c r="D293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
@@ -3561,6 +3858,7 @@
       <c r="C294" t="n">
         <v>0</v>
       </c>
+      <c r="D294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
@@ -3570,6 +3868,7 @@
       <c r="C295" t="n">
         <v>0</v>
       </c>
+      <c r="D295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
@@ -3583,6 +3882,7 @@
       <c r="C296" t="n">
         <v>1</v>
       </c>
+      <c r="D296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
@@ -3596,6 +3896,7 @@
       <c r="C297" t="n">
         <v>1</v>
       </c>
+      <c r="D297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -3605,6 +3906,7 @@
       <c r="C298" t="n">
         <v>0</v>
       </c>
+      <c r="D298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
@@ -3614,6 +3916,7 @@
       <c r="C299" t="n">
         <v>0</v>
       </c>
+      <c r="D299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -3623,6 +3926,7 @@
       <c r="C300" t="n">
         <v>0</v>
       </c>
+      <c r="D300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
@@ -3632,6 +3936,7 @@
       <c r="C301" t="n">
         <v>0</v>
       </c>
+      <c r="D301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
@@ -3641,6 +3946,7 @@
       <c r="C302" t="n">
         <v>0</v>
       </c>
+      <c r="D302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
@@ -3654,6 +3960,7 @@
       <c r="C303" t="n">
         <v>1</v>
       </c>
+      <c r="D303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
@@ -3667,6 +3974,7 @@
       <c r="C304" t="n">
         <v>1</v>
       </c>
+      <c r="D304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n">
@@ -3676,6 +3984,7 @@
       <c r="C305" t="n">
         <v>0</v>
       </c>
+      <c r="D305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n">
@@ -3685,6 +3994,7 @@
       <c r="C306" t="n">
         <v>0</v>
       </c>
+      <c r="D306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
@@ -3694,6 +4004,7 @@
       <c r="C307" t="n">
         <v>0</v>
       </c>
+      <c r="D307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
@@ -3703,6 +4014,7 @@
       <c r="C308" t="n">
         <v>0</v>
       </c>
+      <c r="D308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n">
@@ -3712,6 +4024,7 @@
       <c r="C309" t="n">
         <v>0</v>
       </c>
+      <c r="D309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
@@ -3725,6 +4038,7 @@
       <c r="C310" t="n">
         <v>1</v>
       </c>
+      <c r="D310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n">
@@ -3738,6 +4052,7 @@
       <c r="C311" t="n">
         <v>1</v>
       </c>
+      <c r="D311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n">
@@ -3747,6 +4062,7 @@
       <c r="C312" t="n">
         <v>0</v>
       </c>
+      <c r="D312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n">
@@ -3756,6 +4072,7 @@
       <c r="C313" t="n">
         <v>0</v>
       </c>
+      <c r="D313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n">
@@ -3765,6 +4082,7 @@
       <c r="C314" t="n">
         <v>0</v>
       </c>
+      <c r="D314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n">
@@ -3774,6 +4092,7 @@
       <c r="C315" t="n">
         <v>0</v>
       </c>
+      <c r="D315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n">
@@ -3783,6 +4102,7 @@
       <c r="C316" t="n">
         <v>0</v>
       </c>
+      <c r="D316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n">
@@ -3796,6 +4116,7 @@
       <c r="C317" t="n">
         <v>1</v>
       </c>
+      <c r="D317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n">
@@ -3809,6 +4130,7 @@
       <c r="C318" t="n">
         <v>1</v>
       </c>
+      <c r="D318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n">
@@ -3818,6 +4140,7 @@
       <c r="C319" t="n">
         <v>0</v>
       </c>
+      <c r="D319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n">
@@ -3827,6 +4150,7 @@
       <c r="C320" t="n">
         <v>0</v>
       </c>
+      <c r="D320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n">
@@ -3836,6 +4160,7 @@
       <c r="C321" t="n">
         <v>0</v>
       </c>
+      <c r="D321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n">
@@ -3845,6 +4170,7 @@
       <c r="C322" t="n">
         <v>0</v>
       </c>
+      <c r="D322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n">
@@ -3854,6 +4180,7 @@
       <c r="C323" t="n">
         <v>0</v>
       </c>
+      <c r="D323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n">
@@ -3867,6 +4194,7 @@
       <c r="C324" t="n">
         <v>1</v>
       </c>
+      <c r="D324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n">
@@ -3880,6 +4208,7 @@
       <c r="C325" t="n">
         <v>1</v>
       </c>
+      <c r="D325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n">
@@ -3889,6 +4218,7 @@
       <c r="C326" t="n">
         <v>0</v>
       </c>
+      <c r="D326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n">
@@ -3898,6 +4228,7 @@
       <c r="C327" t="n">
         <v>0</v>
       </c>
+      <c r="D327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n">
@@ -3907,6 +4238,7 @@
       <c r="C328" t="n">
         <v>0</v>
       </c>
+      <c r="D328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n">
@@ -3916,6 +4248,7 @@
       <c r="C329" t="n">
         <v>0</v>
       </c>
+      <c r="D329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n">
@@ -3925,6 +4258,7 @@
       <c r="C330" t="n">
         <v>0</v>
       </c>
+      <c r="D330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n">
@@ -3938,6 +4272,7 @@
       <c r="C331" t="n">
         <v>1</v>
       </c>
+      <c r="D331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n">
@@ -3951,6 +4286,7 @@
       <c r="C332" t="n">
         <v>1</v>
       </c>
+      <c r="D332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n">
@@ -3960,6 +4296,7 @@
       <c r="C333" t="n">
         <v>0</v>
       </c>
+      <c r="D333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n">
@@ -3969,6 +4306,7 @@
       <c r="C334" t="n">
         <v>0</v>
       </c>
+      <c r="D334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -3978,6 +4316,7 @@
       <c r="C335" t="n">
         <v>0</v>
       </c>
+      <c r="D335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -3987,6 +4326,7 @@
       <c r="C336" t="n">
         <v>0</v>
       </c>
+      <c r="D336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -3996,6 +4336,7 @@
       <c r="C337" t="n">
         <v>0</v>
       </c>
+      <c r="D337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -4009,6 +4350,7 @@
       <c r="C338" t="n">
         <v>1</v>
       </c>
+      <c r="D338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -4022,6 +4364,7 @@
       <c r="C339" t="n">
         <v>1</v>
       </c>
+      <c r="D339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -4031,6 +4374,7 @@
       <c r="C340" t="n">
         <v>0</v>
       </c>
+      <c r="D340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -4040,6 +4384,7 @@
       <c r="C341" t="n">
         <v>0</v>
       </c>
+      <c r="D341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -4049,6 +4394,7 @@
       <c r="C342" t="n">
         <v>0</v>
       </c>
+      <c r="D342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -4058,6 +4404,7 @@
       <c r="C343" t="n">
         <v>0</v>
       </c>
+      <c r="D343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -4067,6 +4414,7 @@
       <c r="C344" t="n">
         <v>0</v>
       </c>
+      <c r="D344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -4080,6 +4428,7 @@
       <c r="C345" t="n">
         <v>1</v>
       </c>
+      <c r="D345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -4093,6 +4442,7 @@
       <c r="C346" t="n">
         <v>1</v>
       </c>
+      <c r="D346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -4102,6 +4452,7 @@
       <c r="C347" t="n">
         <v>0</v>
       </c>
+      <c r="D347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -4111,6 +4462,7 @@
       <c r="C348" t="n">
         <v>0</v>
       </c>
+      <c r="D348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -4120,6 +4472,7 @@
       <c r="C349" t="n">
         <v>0</v>
       </c>
+      <c r="D349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -4129,6 +4482,7 @@
       <c r="C350" t="n">
         <v>0</v>
       </c>
+      <c r="D350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -4138,6 +4492,7 @@
       <c r="C351" t="n">
         <v>0</v>
       </c>
+      <c r="D351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -4151,6 +4506,7 @@
       <c r="C352" t="n">
         <v>1</v>
       </c>
+      <c r="D352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -4164,6 +4520,7 @@
       <c r="C353" t="n">
         <v>1</v>
       </c>
+      <c r="D353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -4173,6 +4530,7 @@
       <c r="C354" t="n">
         <v>0</v>
       </c>
+      <c r="D354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -4182,6 +4540,7 @@
       <c r="C355" t="n">
         <v>0</v>
       </c>
+      <c r="D355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -4191,6 +4550,7 @@
       <c r="C356" t="n">
         <v>0</v>
       </c>
+      <c r="D356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -4200,6 +4560,7 @@
       <c r="C357" t="n">
         <v>0</v>
       </c>
+      <c r="D357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -4209,6 +4570,7 @@
       <c r="C358" t="n">
         <v>0</v>
       </c>
+      <c r="D358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -4222,6 +4584,7 @@
       <c r="C359" t="n">
         <v>1</v>
       </c>
+      <c r="D359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -4235,6 +4598,7 @@
       <c r="C360" t="n">
         <v>1</v>
       </c>
+      <c r="D360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -4248,6 +4612,7 @@
       <c r="C361" t="n">
         <v>1</v>
       </c>
+      <c r="D361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -4261,6 +4626,7 @@
       <c r="C362" t="n">
         <v>1</v>
       </c>
+      <c r="D362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -4274,6 +4640,7 @@
       <c r="C363" t="n">
         <v>1</v>
       </c>
+      <c r="D363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -4287,6 +4654,7 @@
       <c r="C364" t="n">
         <v>1</v>
       </c>
+      <c r="D364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -4300,6 +4668,7 @@
       <c r="C365" t="n">
         <v>1</v>
       </c>
+      <c r="D365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -4313,6 +4682,7 @@
       <c r="C366" t="n">
         <v>1</v>
       </c>
+      <c r="D366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -4326,6 +4696,7 @@
       <c r="C367" t="n">
         <v>1</v>
       </c>
+      <c r="D367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -4335,6 +4706,7 @@
       <c r="C368" t="n">
         <v>0</v>
       </c>
+      <c r="D368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -4344,6 +4716,7 @@
       <c r="C369" t="n">
         <v>0</v>
       </c>
+      <c r="D369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -4353,6 +4726,7 @@
       <c r="C370" t="n">
         <v>0</v>
       </c>
+      <c r="D370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -4362,6 +4736,7 @@
       <c r="C371" t="n">
         <v>0</v>
       </c>
+      <c r="D371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -4371,6 +4746,7 @@
       <c r="C372" t="n">
         <v>0</v>
       </c>
+      <c r="D372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -4384,6 +4760,7 @@
       <c r="C373" t="n">
         <v>1</v>
       </c>
+      <c r="D373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -4397,6 +4774,7 @@
       <c r="C374" t="n">
         <v>1</v>
       </c>
+      <c r="D374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -4406,6 +4784,7 @@
       <c r="C375" t="n">
         <v>0</v>
       </c>
+      <c r="D375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -4415,6 +4794,7 @@
       <c r="C376" t="n">
         <v>0</v>
       </c>
+      <c r="D376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -4424,6 +4804,7 @@
       <c r="C377" t="n">
         <v>0</v>
       </c>
+      <c r="D377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -4433,6 +4814,7 @@
       <c r="C378" t="n">
         <v>0</v>
       </c>
+      <c r="D378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -4442,6 +4824,7 @@
       <c r="C379" t="n">
         <v>0</v>
       </c>
+      <c r="D379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -4455,6 +4838,7 @@
       <c r="C380" t="n">
         <v>1</v>
       </c>
+      <c r="D380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -4468,6 +4852,7 @@
       <c r="C381" t="n">
         <v>1</v>
       </c>
+      <c r="D381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -4477,6 +4862,7 @@
       <c r="C382" t="n">
         <v>0</v>
       </c>
+      <c r="D382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -4486,6 +4872,7 @@
       <c r="C383" t="n">
         <v>0</v>
       </c>
+      <c r="D383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -4495,6 +4882,7 @@
       <c r="C384" t="n">
         <v>0</v>
       </c>
+      <c r="D384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -4504,6 +4892,7 @@
       <c r="C385" t="n">
         <v>0</v>
       </c>
+      <c r="D385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -4513,6 +4902,7 @@
       <c r="C386" t="n">
         <v>0</v>
       </c>
+      <c r="D386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -4526,6 +4916,7 @@
       <c r="C387" t="n">
         <v>1</v>
       </c>
+      <c r="D387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -4539,6 +4930,7 @@
       <c r="C388" t="n">
         <v>1</v>
       </c>
+      <c r="D388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -4552,6 +4944,7 @@
       <c r="C389" t="n">
         <v>1</v>
       </c>
+      <c r="D389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -4561,6 +4954,7 @@
       <c r="C390" t="n">
         <v>0</v>
       </c>
+      <c r="D390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -4570,6 +4964,7 @@
       <c r="C391" t="n">
         <v>0</v>
       </c>
+      <c r="D391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -4579,6 +4974,7 @@
       <c r="C392" t="n">
         <v>0</v>
       </c>
+      <c r="D392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -4588,6 +4984,7 @@
       <c r="C393" t="n">
         <v>0</v>
       </c>
+      <c r="D393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -4601,6 +4998,7 @@
       <c r="C394" t="n">
         <v>1</v>
       </c>
+      <c r="D394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -4614,6 +5012,7 @@
       <c r="C395" t="n">
         <v>1</v>
       </c>
+      <c r="D395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -4623,6 +5022,7 @@
       <c r="C396" t="n">
         <v>0</v>
       </c>
+      <c r="D396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -4632,6 +5032,7 @@
       <c r="C397" t="n">
         <v>0</v>
       </c>
+      <c r="D397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -4641,6 +5042,7 @@
       <c r="C398" t="n">
         <v>0</v>
       </c>
+      <c r="D398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -4650,6 +5052,7 @@
       <c r="C399" t="n">
         <v>0</v>
       </c>
+      <c r="D399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -4659,6 +5062,7 @@
       <c r="C400" t="n">
         <v>0</v>
       </c>
+      <c r="D400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -4672,6 +5076,7 @@
       <c r="C401" t="n">
         <v>1</v>
       </c>
+      <c r="D401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -4685,6 +5090,7 @@
       <c r="C402" t="n">
         <v>1</v>
       </c>
+      <c r="D402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -4694,6 +5100,7 @@
       <c r="C403" t="n">
         <v>0</v>
       </c>
+      <c r="D403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -4703,6 +5110,7 @@
       <c r="C404" t="n">
         <v>0</v>
       </c>
+      <c r="D404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -4712,6 +5120,7 @@
       <c r="C405" t="n">
         <v>0</v>
       </c>
+      <c r="D405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -4721,6 +5130,7 @@
       <c r="C406" t="n">
         <v>0</v>
       </c>
+      <c r="D406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -4730,6 +5140,7 @@
       <c r="C407" t="n">
         <v>0</v>
       </c>
+      <c r="D407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -4743,6 +5154,7 @@
       <c r="C408" t="n">
         <v>1</v>
       </c>
+      <c r="D408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -4756,6 +5168,7 @@
       <c r="C409" t="n">
         <v>1</v>
       </c>
+      <c r="D409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -4765,6 +5178,7 @@
       <c r="C410" t="n">
         <v>0</v>
       </c>
+      <c r="D410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -4774,6 +5188,7 @@
       <c r="C411" t="n">
         <v>0</v>
       </c>
+      <c r="D411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -4783,6 +5198,7 @@
       <c r="C412" t="n">
         <v>0</v>
       </c>
+      <c r="D412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -4792,6 +5208,7 @@
       <c r="C413" t="n">
         <v>0</v>
       </c>
+      <c r="D413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -4801,6 +5218,7 @@
       <c r="C414" t="n">
         <v>0</v>
       </c>
+      <c r="D414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -4814,6 +5232,7 @@
       <c r="C415" t="n">
         <v>1</v>
       </c>
+      <c r="D415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -4827,6 +5246,7 @@
       <c r="C416" t="n">
         <v>1</v>
       </c>
+      <c r="D416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -4836,6 +5256,7 @@
       <c r="C417" t="n">
         <v>0</v>
       </c>
+      <c r="D417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -4845,6 +5266,7 @@
       <c r="C418" t="n">
         <v>0</v>
       </c>
+      <c r="D418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -4854,6 +5276,7 @@
       <c r="C419" t="n">
         <v>0</v>
       </c>
+      <c r="D419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -4863,6 +5286,7 @@
       <c r="C420" t="n">
         <v>0</v>
       </c>
+      <c r="D420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -4872,6 +5296,7 @@
       <c r="C421" t="n">
         <v>0</v>
       </c>
+      <c r="D421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -4885,6 +5310,7 @@
       <c r="C422" t="n">
         <v>1</v>
       </c>
+      <c r="D422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -4898,6 +5324,7 @@
       <c r="C423" t="n">
         <v>1</v>
       </c>
+      <c r="D423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -4907,6 +5334,7 @@
       <c r="C424" t="n">
         <v>0</v>
       </c>
+      <c r="D424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -4916,6 +5344,7 @@
       <c r="C425" t="n">
         <v>0</v>
       </c>
+      <c r="D425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -4925,6 +5354,7 @@
       <c r="C426" t="n">
         <v>0</v>
       </c>
+      <c r="D426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -4934,6 +5364,7 @@
       <c r="C427" t="n">
         <v>0</v>
       </c>
+      <c r="D427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -4943,6 +5374,7 @@
       <c r="C428" t="n">
         <v>0</v>
       </c>
+      <c r="D428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -4956,6 +5388,7 @@
       <c r="C429" t="n">
         <v>1</v>
       </c>
+      <c r="D429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -4969,6 +5402,7 @@
       <c r="C430" t="n">
         <v>1</v>
       </c>
+      <c r="D430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -4978,6 +5412,7 @@
       <c r="C431" t="n">
         <v>0</v>
       </c>
+      <c r="D431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -4987,6 +5422,7 @@
       <c r="C432" t="n">
         <v>0</v>
       </c>
+      <c r="D432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -4996,6 +5432,7 @@
       <c r="C433" t="n">
         <v>0</v>
       </c>
+      <c r="D433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -5005,6 +5442,7 @@
       <c r="C434" t="n">
         <v>0</v>
       </c>
+      <c r="D434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -5014,6 +5452,7 @@
       <c r="C435" t="n">
         <v>0</v>
       </c>
+      <c r="D435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -5027,6 +5466,7 @@
       <c r="C436" t="n">
         <v>1</v>
       </c>
+      <c r="D436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -5040,6 +5480,7 @@
       <c r="C437" t="n">
         <v>1</v>
       </c>
+      <c r="D437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -5049,6 +5490,7 @@
       <c r="C438" t="n">
         <v>0</v>
       </c>
+      <c r="D438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -5058,6 +5500,7 @@
       <c r="C439" t="n">
         <v>0</v>
       </c>
+      <c r="D439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -5067,6 +5510,7 @@
       <c r="C440" t="n">
         <v>0</v>
       </c>
+      <c r="D440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -5076,6 +5520,7 @@
       <c r="C441" t="n">
         <v>0</v>
       </c>
+      <c r="D441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -5085,6 +5530,7 @@
       <c r="C442" t="n">
         <v>0</v>
       </c>
+      <c r="D442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -5098,6 +5544,7 @@
       <c r="C443" t="n">
         <v>1</v>
       </c>
+      <c r="D443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -5111,6 +5558,7 @@
       <c r="C444" t="n">
         <v>1</v>
       </c>
+      <c r="D444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -5120,6 +5568,7 @@
       <c r="C445" t="n">
         <v>0</v>
       </c>
+      <c r="D445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -5129,6 +5578,7 @@
       <c r="C446" t="n">
         <v>0</v>
       </c>
+      <c r="D446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -5142,6 +5592,7 @@
       <c r="C447" t="n">
         <v>1</v>
       </c>
+      <c r="D447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -5155,6 +5606,7 @@
       <c r="C448" t="n">
         <v>1</v>
       </c>
+      <c r="D448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -5164,6 +5616,7 @@
       <c r="C449" t="n">
         <v>0</v>
       </c>
+      <c r="D449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -5177,6 +5630,7 @@
       <c r="C450" t="n">
         <v>1</v>
       </c>
+      <c r="D450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -5190,6 +5644,7 @@
       <c r="C451" t="n">
         <v>1</v>
       </c>
+      <c r="D451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -5199,6 +5654,7 @@
       <c r="C452" t="n">
         <v>0</v>
       </c>
+      <c r="D452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -5208,6 +5664,7 @@
       <c r="C453" t="n">
         <v>0</v>
       </c>
+      <c r="D453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -5217,6 +5674,7 @@
       <c r="C454" t="n">
         <v>0</v>
       </c>
+      <c r="D454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -5226,6 +5684,7 @@
       <c r="C455" t="n">
         <v>0</v>
       </c>
+      <c r="D455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -5235,6 +5694,7 @@
       <c r="C456" t="n">
         <v>0</v>
       </c>
+      <c r="D456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -5248,6 +5708,7 @@
       <c r="C457" t="n">
         <v>1</v>
       </c>
+      <c r="D457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -5261,6 +5722,7 @@
       <c r="C458" t="n">
         <v>1</v>
       </c>
+      <c r="D458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -5270,6 +5732,7 @@
       <c r="C459" t="n">
         <v>0</v>
       </c>
+      <c r="D459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -5279,6 +5742,7 @@
       <c r="C460" t="n">
         <v>0</v>
       </c>
+      <c r="D460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -5288,6 +5752,7 @@
       <c r="C461" t="n">
         <v>0</v>
       </c>
+      <c r="D461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -5297,6 +5762,7 @@
       <c r="C462" t="n">
         <v>0</v>
       </c>
+      <c r="D462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -5310,6 +5776,7 @@
       <c r="C463" t="n">
         <v>1</v>
       </c>
+      <c r="D463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -5323,6 +5790,7 @@
       <c r="C464" t="n">
         <v>1</v>
       </c>
+      <c r="D464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -5336,6 +5804,7 @@
       <c r="C465" t="n">
         <v>1</v>
       </c>
+      <c r="D465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -5345,6 +5814,7 @@
       <c r="C466" t="n">
         <v>0</v>
       </c>
+      <c r="D466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -5354,6 +5824,7 @@
       <c r="C467" t="n">
         <v>0</v>
       </c>
+      <c r="D467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -5363,6 +5834,7 @@
       <c r="C468" t="n">
         <v>0</v>
       </c>
+      <c r="D468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -5372,6 +5844,7 @@
       <c r="C469" t="n">
         <v>0</v>
       </c>
+      <c r="D469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -5381,6 +5854,7 @@
       <c r="C470" t="n">
         <v>0</v>
       </c>
+      <c r="D470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -5394,6 +5868,7 @@
       <c r="C471" t="n">
         <v>1</v>
       </c>
+      <c r="D471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -5407,6 +5882,7 @@
       <c r="C472" t="n">
         <v>1</v>
       </c>
+      <c r="D472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -5416,6 +5892,7 @@
       <c r="C473" t="n">
         <v>0</v>
       </c>
+      <c r="D473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -5425,6 +5902,7 @@
       <c r="C474" t="n">
         <v>0</v>
       </c>
+      <c r="D474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -5438,6 +5916,7 @@
       <c r="C475" t="n">
         <v>1</v>
       </c>
+      <c r="D475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -5451,6 +5930,7 @@
       <c r="C476" t="n">
         <v>1</v>
       </c>
+      <c r="D476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -5464,6 +5944,7 @@
       <c r="C477" t="n">
         <v>1</v>
       </c>
+      <c r="D477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -5477,6 +5958,7 @@
       <c r="C478" t="n">
         <v>1</v>
       </c>
+      <c r="D478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -5490,6 +5972,7 @@
       <c r="C479" t="n">
         <v>1</v>
       </c>
+      <c r="D479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -5503,6 +5986,7 @@
       <c r="C480" t="n">
         <v>1</v>
       </c>
+      <c r="D480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -5516,6 +6000,7 @@
       <c r="C481" t="n">
         <v>1</v>
       </c>
+      <c r="D481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -5525,6 +6010,7 @@
       <c r="C482" t="n">
         <v>0</v>
       </c>
+      <c r="D482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -5534,6 +6020,7 @@
       <c r="C483" t="n">
         <v>0</v>
       </c>
+      <c r="D483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -5543,6 +6030,7 @@
       <c r="C484" t="n">
         <v>0</v>
       </c>
+      <c r="D484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -5556,6 +6044,7 @@
       <c r="C485" t="n">
         <v>1</v>
       </c>
+      <c r="D485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -5569,6 +6058,7 @@
       <c r="C486" t="n">
         <v>1</v>
       </c>
+      <c r="D486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -5582,6 +6072,7 @@
       <c r="C487" t="n">
         <v>1</v>
       </c>
+      <c r="D487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -5591,6 +6082,7 @@
       <c r="C488" t="n">
         <v>0</v>
       </c>
+      <c r="D488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
@@ -5600,6 +6092,7 @@
       <c r="C489" t="n">
         <v>0</v>
       </c>
+      <c r="D489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -5609,6 +6102,7 @@
       <c r="C490" t="n">
         <v>0</v>
       </c>
+      <c r="D490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
@@ -5618,6 +6112,7 @@
       <c r="C491" t="n">
         <v>0</v>
       </c>
+      <c r="D491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -5631,6 +6126,7 @@
       <c r="C492" t="n">
         <v>1</v>
       </c>
+      <c r="D492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -5644,6 +6140,7 @@
       <c r="C493" t="n">
         <v>1</v>
       </c>
+      <c r="D493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -5653,6 +6150,7 @@
       <c r="C494" t="n">
         <v>0</v>
       </c>
+      <c r="D494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -5662,6 +6160,7 @@
       <c r="C495" t="n">
         <v>0</v>
       </c>
+      <c r="D495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
@@ -5671,6 +6170,7 @@
       <c r="C496" t="n">
         <v>0</v>
       </c>
+      <c r="D496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -5680,6 +6180,7 @@
       <c r="C497" t="n">
         <v>0</v>
       </c>
+      <c r="D497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -5689,6 +6190,7 @@
       <c r="C498" t="n">
         <v>0</v>
       </c>
+      <c r="D498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
@@ -5702,6 +6204,7 @@
       <c r="C499" t="n">
         <v>1</v>
       </c>
+      <c r="D499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -5715,6 +6218,7 @@
       <c r="C500" t="n">
         <v>1</v>
       </c>
+      <c r="D500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -5724,6 +6228,7 @@
       <c r="C501" t="n">
         <v>0</v>
       </c>
+      <c r="D501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
@@ -5733,6 +6238,7 @@
       <c r="C502" t="n">
         <v>0</v>
       </c>
+      <c r="D502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -5742,6 +6248,7 @@
       <c r="C503" t="n">
         <v>0</v>
       </c>
+      <c r="D503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
@@ -5755,6 +6262,7 @@
       <c r="C504" t="n">
         <v>1</v>
       </c>
+      <c r="D504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
@@ -5764,6 +6272,7 @@
       <c r="C505" t="n">
         <v>0</v>
       </c>
+      <c r="D505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -5777,6 +6286,7 @@
       <c r="C506" t="n">
         <v>1</v>
       </c>
+      <c r="D506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -5790,6 +6300,7 @@
       <c r="C507" t="n">
         <v>1</v>
       </c>
+      <c r="D507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -5799,6 +6310,7 @@
       <c r="C508" t="n">
         <v>0</v>
       </c>
+      <c r="D508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -5808,6 +6320,7 @@
       <c r="C509" t="n">
         <v>0</v>
       </c>
+      <c r="D509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
@@ -5817,6 +6330,7 @@
       <c r="C510" t="n">
         <v>0</v>
       </c>
+      <c r="D510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -5826,6 +6340,7 @@
       <c r="C511" t="n">
         <v>0</v>
       </c>
+      <c r="D511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
@@ -5835,6 +6350,7 @@
       <c r="C512" t="n">
         <v>0</v>
       </c>
+      <c r="D512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
@@ -5848,6 +6364,7 @@
       <c r="C513" t="n">
         <v>1</v>
       </c>
+      <c r="D513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -5861,6 +6378,7 @@
       <c r="C514" t="n">
         <v>1</v>
       </c>
+      <c r="D514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -5870,6 +6388,7 @@
       <c r="C515" t="n">
         <v>0</v>
       </c>
+      <c r="D515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
@@ -5879,6 +6398,7 @@
       <c r="C516" t="n">
         <v>0</v>
       </c>
+      <c r="D516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -5888,6 +6408,7 @@
       <c r="C517" t="n">
         <v>0</v>
       </c>
+      <c r="D517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
@@ -5901,6 +6422,7 @@
       <c r="C518" t="n">
         <v>1</v>
       </c>
+      <c r="D518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -5914,6 +6436,7 @@
       <c r="C519" t="n">
         <v>1</v>
       </c>
+      <c r="D519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
@@ -5927,6 +6450,7 @@
       <c r="C520" t="n">
         <v>1</v>
       </c>
+      <c r="D520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -5940,6 +6464,7 @@
       <c r="C521" t="n">
         <v>1</v>
       </c>
+      <c r="D521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
@@ -5949,6 +6474,7 @@
       <c r="C522" t="n">
         <v>0</v>
       </c>
+      <c r="D522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -5958,6 +6484,7 @@
       <c r="C523" t="n">
         <v>0</v>
       </c>
+      <c r="D523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -5967,6 +6494,7 @@
       <c r="C524" t="n">
         <v>0</v>
       </c>
+      <c r="D524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -5976,6 +6504,7 @@
       <c r="C525" t="n">
         <v>0</v>
       </c>
+      <c r="D525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
@@ -5985,6 +6514,7 @@
       <c r="C526" t="n">
         <v>0</v>
       </c>
+      <c r="D526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
@@ -5998,6 +6528,7 @@
       <c r="C527" t="n">
         <v>1</v>
       </c>
+      <c r="D527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -6011,6 +6542,7 @@
       <c r="C528" t="n">
         <v>1</v>
       </c>
+      <c r="D528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="n">
@@ -6020,6 +6552,7 @@
       <c r="C529" t="n">
         <v>0</v>
       </c>
+      <c r="D529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="n">
@@ -6029,6 +6562,7 @@
       <c r="C530" t="n">
         <v>0</v>
       </c>
+      <c r="D530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="n">
@@ -6038,6 +6572,7 @@
       <c r="C531" t="n">
         <v>0</v>
       </c>
+      <c r="D531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="n">
@@ -6047,6 +6582,7 @@
       <c r="C532" t="n">
         <v>0</v>
       </c>
+      <c r="D532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="n">
@@ -6056,6 +6592,7 @@
       <c r="C533" t="n">
         <v>0</v>
       </c>
+      <c r="D533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="n">
@@ -6069,6 +6606,7 @@
       <c r="C534" t="n">
         <v>1</v>
       </c>
+      <c r="D534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="n">
@@ -6082,6 +6620,7 @@
       <c r="C535" t="n">
         <v>1</v>
       </c>
+      <c r="D535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="n">
@@ -6091,6 +6630,7 @@
       <c r="C536" t="n">
         <v>0</v>
       </c>
+      <c r="D536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="n">
@@ -6100,6 +6640,7 @@
       <c r="C537" t="n">
         <v>0</v>
       </c>
+      <c r="D537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="n">
@@ -6109,6 +6650,7 @@
       <c r="C538" t="n">
         <v>0</v>
       </c>
+      <c r="D538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="n">
@@ -6118,6 +6660,7 @@
       <c r="C539" t="n">
         <v>0</v>
       </c>
+      <c r="D539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="n">
@@ -6127,6 +6670,7 @@
       <c r="C540" t="n">
         <v>0</v>
       </c>
+      <c r="D540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="n">
@@ -6140,6 +6684,7 @@
       <c r="C541" t="n">
         <v>1</v>
       </c>
+      <c r="D541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="n">
@@ -6153,6 +6698,7 @@
       <c r="C542" t="n">
         <v>1</v>
       </c>
+      <c r="D542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="n">
@@ -6166,6 +6712,7 @@
       <c r="C543" t="n">
         <v>1</v>
       </c>
+      <c r="D543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="n">
@@ -6179,6 +6726,7 @@
       <c r="C544" t="n">
         <v>1</v>
       </c>
+      <c r="D544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="n">
@@ -6192,6 +6740,7 @@
       <c r="C545" t="n">
         <v>1</v>
       </c>
+      <c r="D545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="n">
@@ -6205,6 +6754,7 @@
       <c r="C546" t="n">
         <v>1</v>
       </c>
+      <c r="D546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="n">
@@ -6218,6 +6768,7 @@
       <c r="C547" t="n">
         <v>1</v>
       </c>
+      <c r="D547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="n">
@@ -6231,6 +6782,7 @@
       <c r="C548" t="n">
         <v>1</v>
       </c>
+      <c r="D548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="n">
@@ -6244,6 +6796,7 @@
       <c r="C549" t="n">
         <v>1</v>
       </c>
+      <c r="D549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="n">
@@ -6257,6 +6810,7 @@
       <c r="C550" t="n">
         <v>1</v>
       </c>
+      <c r="D550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="n">
@@ -6270,6 +6824,7 @@
       <c r="C551" t="n">
         <v>1</v>
       </c>
+      <c r="D551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="n">
@@ -6283,6 +6838,7 @@
       <c r="C552" t="n">
         <v>1</v>
       </c>
+      <c r="D552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="n">
@@ -6296,6 +6852,7 @@
       <c r="C553" t="n">
         <v>1</v>
       </c>
+      <c r="D553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="n">
@@ -6309,6 +6866,7 @@
       <c r="C554" t="n">
         <v>1</v>
       </c>
+      <c r="D554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="n">
@@ -6322,6 +6880,7 @@
       <c r="C555" t="n">
         <v>1</v>
       </c>
+      <c r="D555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="n">
@@ -6335,6 +6894,7 @@
       <c r="C556" t="n">
         <v>1</v>
       </c>
+      <c r="D556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="n">
@@ -6348,6 +6908,7 @@
       <c r="C557" t="n">
         <v>1</v>
       </c>
+      <c r="D557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="n">
@@ -6361,6 +6922,7 @@
       <c r="C558" t="n">
         <v>1</v>
       </c>
+      <c r="D558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="n">
@@ -6374,6 +6936,7 @@
       <c r="C559" t="n">
         <v>1</v>
       </c>
+      <c r="D559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="n">
@@ -6387,6 +6950,7 @@
       <c r="C560" t="n">
         <v>1</v>
       </c>
+      <c r="D560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="n">
@@ -6400,6 +6964,7 @@
       <c r="C561" t="n">
         <v>1</v>
       </c>
+      <c r="D561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="n">
@@ -6413,6 +6978,7 @@
       <c r="C562" t="n">
         <v>1</v>
       </c>
+      <c r="D562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="n">
@@ -6426,6 +6992,7 @@
       <c r="C563" t="n">
         <v>1</v>
       </c>
+      <c r="D563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="n">
@@ -6435,6 +7002,7 @@
       <c r="C564" t="n">
         <v>0</v>
       </c>
+      <c r="D564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="n">
@@ -6444,6 +7012,7 @@
       <c r="C565" t="n">
         <v>0</v>
       </c>
+      <c r="D565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="n">
@@ -6457,6 +7026,7 @@
       <c r="C566" t="n">
         <v>1</v>
       </c>
+      <c r="D566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="n">
@@ -6466,6 +7036,7 @@
       <c r="C567" t="n">
         <v>0</v>
       </c>
+      <c r="D567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="n">
@@ -6475,6 +7046,7 @@
       <c r="C568" t="n">
         <v>0</v>
       </c>
+      <c r="D568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="n">
@@ -6488,6 +7060,7 @@
       <c r="C569" t="n">
         <v>1</v>
       </c>
+      <c r="D569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="n">
@@ -6501,6 +7074,7 @@
       <c r="C570" t="n">
         <v>1</v>
       </c>
+      <c r="D570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="n">
@@ -6510,6 +7084,7 @@
       <c r="C571" t="n">
         <v>0</v>
       </c>
+      <c r="D571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="n">
@@ -6519,6 +7094,7 @@
       <c r="C572" t="n">
         <v>0</v>
       </c>
+      <c r="D572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="n">
@@ -6528,6 +7104,7 @@
       <c r="C573" t="n">
         <v>0</v>
       </c>
+      <c r="D573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="n">
@@ -6537,6 +7114,7 @@
       <c r="C574" t="n">
         <v>0</v>
       </c>
+      <c r="D574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="n">
@@ -6546,6 +7124,7 @@
       <c r="C575" t="n">
         <v>0</v>
       </c>
+      <c r="D575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="n">
@@ -6559,6 +7138,7 @@
       <c r="C576" t="n">
         <v>1</v>
       </c>
+      <c r="D576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="n">
@@ -6572,6 +7152,7 @@
       <c r="C577" t="n">
         <v>1</v>
       </c>
+      <c r="D577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="n">
@@ -6581,6 +7162,7 @@
       <c r="C578" t="n">
         <v>0</v>
       </c>
+      <c r="D578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="n">
@@ -6590,6 +7172,7 @@
       <c r="C579" t="n">
         <v>0</v>
       </c>
+      <c r="D579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="n">
@@ -6599,6 +7182,7 @@
       <c r="C580" t="n">
         <v>0</v>
       </c>
+      <c r="D580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="n">
@@ -6608,6 +7192,7 @@
       <c r="C581" t="n">
         <v>0</v>
       </c>
+      <c r="D581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="n">
@@ -6617,6 +7202,7 @@
       <c r="C582" t="n">
         <v>0</v>
       </c>
+      <c r="D582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="n">
@@ -6630,6 +7216,7 @@
       <c r="C583" t="n">
         <v>1</v>
       </c>
+      <c r="D583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="n">
@@ -6643,6 +7230,7 @@
       <c r="C584" t="n">
         <v>1</v>
       </c>
+      <c r="D584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="n">
@@ -6652,6 +7240,7 @@
       <c r="C585" t="n">
         <v>0</v>
       </c>
+      <c r="D585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="n">
@@ -6661,6 +7250,7 @@
       <c r="C586" t="n">
         <v>0</v>
       </c>
+      <c r="D586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="n">
@@ -6670,6 +7260,7 @@
       <c r="C587" t="n">
         <v>0</v>
       </c>
+      <c r="D587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="n">
@@ -6679,6 +7270,7 @@
       <c r="C588" t="n">
         <v>0</v>
       </c>
+      <c r="D588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="n">
@@ -6688,6 +7280,7 @@
       <c r="C589" t="n">
         <v>0</v>
       </c>
+      <c r="D589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="n">
@@ -6701,6 +7294,7 @@
       <c r="C590" t="n">
         <v>1</v>
       </c>
+      <c r="D590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="n">
@@ -6714,6 +7308,7 @@
       <c r="C591" t="n">
         <v>1</v>
       </c>
+      <c r="D591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="n">
@@ -6723,6 +7318,7 @@
       <c r="C592" t="n">
         <v>0</v>
       </c>
+      <c r="D592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="n">
@@ -6732,6 +7328,7 @@
       <c r="C593" t="n">
         <v>0</v>
       </c>
+      <c r="D593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="n">
@@ -6741,6 +7338,7 @@
       <c r="C594" t="n">
         <v>0</v>
       </c>
+      <c r="D594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="n">
@@ -6754,6 +7352,7 @@
       <c r="C595" t="n">
         <v>1</v>
       </c>
+      <c r="D595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="n">
@@ -6763,6 +7362,7 @@
       <c r="C596" t="n">
         <v>0</v>
       </c>
+      <c r="D596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="n">
@@ -6776,6 +7376,7 @@
       <c r="C597" t="n">
         <v>1</v>
       </c>
+      <c r="D597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="n">
@@ -6789,6 +7390,7 @@
       <c r="C598" t="n">
         <v>1</v>
       </c>
+      <c r="D598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="n">
@@ -6798,6 +7400,7 @@
       <c r="C599" t="n">
         <v>0</v>
       </c>
+      <c r="D599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="n">
@@ -6807,6 +7410,7 @@
       <c r="C600" t="n">
         <v>0</v>
       </c>
+      <c r="D600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="n">
@@ -6816,6 +7420,7 @@
       <c r="C601" t="n">
         <v>0</v>
       </c>
+      <c r="D601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="n">
@@ -6825,6 +7430,7 @@
       <c r="C602" t="n">
         <v>0</v>
       </c>
+      <c r="D602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="n">
@@ -6834,6 +7440,7 @@
       <c r="C603" t="n">
         <v>0</v>
       </c>
+      <c r="D603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="n">
@@ -6847,6 +7454,7 @@
       <c r="C604" t="n">
         <v>1</v>
       </c>
+      <c r="D604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="n">
@@ -6860,6 +7468,7 @@
       <c r="C605" t="n">
         <v>1</v>
       </c>
+      <c r="D605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="n">
@@ -6869,6 +7478,7 @@
       <c r="C606" t="n">
         <v>0</v>
       </c>
+      <c r="D606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="n">
@@ -6878,6 +7488,7 @@
       <c r="C607" t="n">
         <v>0</v>
       </c>
+      <c r="D607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="n">
@@ -6887,6 +7498,7 @@
       <c r="C608" t="n">
         <v>0</v>
       </c>
+      <c r="D608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="n">
@@ -6896,6 +7508,7 @@
       <c r="C609" t="n">
         <v>0</v>
       </c>
+      <c r="D609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="n">
@@ -6905,6 +7518,7 @@
       <c r="C610" t="n">
         <v>0</v>
       </c>
+      <c r="D610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="n">
@@ -6918,6 +7532,7 @@
       <c r="C611" t="n">
         <v>1</v>
       </c>
+      <c r="D611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="n">
@@ -6931,6 +7546,7 @@
       <c r="C612" t="n">
         <v>1</v>
       </c>
+      <c r="D612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="n">
@@ -6940,6 +7556,7 @@
       <c r="C613" t="n">
         <v>0</v>
       </c>
+      <c r="D613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="n">
@@ -6949,6 +7566,7 @@
       <c r="C614" t="n">
         <v>0</v>
       </c>
+      <c r="D614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="n">
@@ -6958,6 +7576,7 @@
       <c r="C615" t="n">
         <v>0</v>
       </c>
+      <c r="D615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="n">
@@ -6967,6 +7586,7 @@
       <c r="C616" t="n">
         <v>0</v>
       </c>
+      <c r="D616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="n">
@@ -6976,6 +7596,7 @@
       <c r="C617" t="n">
         <v>0</v>
       </c>
+      <c r="D617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="n">
@@ -6989,6 +7610,7 @@
       <c r="C618" t="n">
         <v>1</v>
       </c>
+      <c r="D618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="n">
@@ -7002,6 +7624,7 @@
       <c r="C619" t="n">
         <v>1</v>
       </c>
+      <c r="D619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="n">
@@ -7011,6 +7634,7 @@
       <c r="C620" t="n">
         <v>0</v>
       </c>
+      <c r="D620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="n">
@@ -7020,6 +7644,7 @@
       <c r="C621" t="n">
         <v>0</v>
       </c>
+      <c r="D621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="n">
@@ -7029,6 +7654,7 @@
       <c r="C622" t="n">
         <v>0</v>
       </c>
+      <c r="D622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="n">
@@ -7038,6 +7664,7 @@
       <c r="C623" t="n">
         <v>0</v>
       </c>
+      <c r="D623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="n">
@@ -7047,6 +7674,7 @@
       <c r="C624" t="n">
         <v>0</v>
       </c>
+      <c r="D624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="n">
@@ -7060,6 +7688,7 @@
       <c r="C625" t="n">
         <v>1</v>
       </c>
+      <c r="D625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="n">
@@ -7073,6 +7702,7 @@
       <c r="C626" t="n">
         <v>1</v>
       </c>
+      <c r="D626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="n">
@@ -7082,6 +7712,7 @@
       <c r="C627" t="n">
         <v>0</v>
       </c>
+      <c r="D627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="n">
@@ -7091,6 +7722,7 @@
       <c r="C628" t="n">
         <v>0</v>
       </c>
+      <c r="D628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="n">
@@ -7100,6 +7732,7 @@
       <c r="C629" t="n">
         <v>0</v>
       </c>
+      <c r="D629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="n">
@@ -7109,6 +7742,7 @@
       <c r="C630" t="n">
         <v>0</v>
       </c>
+      <c r="D630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="n">
@@ -7118,6 +7752,7 @@
       <c r="C631" t="n">
         <v>0</v>
       </c>
+      <c r="D631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="n">
@@ -7131,6 +7766,7 @@
       <c r="C632" t="n">
         <v>1</v>
       </c>
+      <c r="D632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="n">
@@ -7144,6 +7780,7 @@
       <c r="C633" t="n">
         <v>1</v>
       </c>
+      <c r="D633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="n">
@@ -7153,6 +7790,7 @@
       <c r="C634" t="n">
         <v>0</v>
       </c>
+      <c r="D634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="n">
@@ -7162,6 +7800,7 @@
       <c r="C635" t="n">
         <v>0</v>
       </c>
+      <c r="D635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="n">
@@ -7171,6 +7810,7 @@
       <c r="C636" t="n">
         <v>0</v>
       </c>
+      <c r="D636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="n">
@@ -7184,6 +7824,7 @@
       <c r="C637" t="n">
         <v>1</v>
       </c>
+      <c r="D637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="n">
@@ -7193,6 +7834,7 @@
       <c r="C638" t="n">
         <v>0</v>
       </c>
+      <c r="D638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="n">
@@ -7206,6 +7848,7 @@
       <c r="C639" t="n">
         <v>1</v>
       </c>
+      <c r="D639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="n">
@@ -7219,6 +7862,7 @@
       <c r="C640" t="n">
         <v>1</v>
       </c>
+      <c r="D640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="n">
@@ -7228,6 +7872,7 @@
       <c r="C641" t="n">
         <v>0</v>
       </c>
+      <c r="D641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="n">
@@ -7237,6 +7882,7 @@
       <c r="C642" t="n">
         <v>0</v>
       </c>
+      <c r="D642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="n">
@@ -7246,6 +7892,7 @@
       <c r="C643" t="n">
         <v>0</v>
       </c>
+      <c r="D643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="n">
@@ -7255,6 +7902,7 @@
       <c r="C644" t="n">
         <v>0</v>
       </c>
+      <c r="D644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="n">
@@ -7264,6 +7912,7 @@
       <c r="C645" t="n">
         <v>0</v>
       </c>
+      <c r="D645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="n">
@@ -7277,6 +7926,7 @@
       <c r="C646" t="n">
         <v>1</v>
       </c>
+      <c r="D646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="n">
@@ -7290,6 +7940,7 @@
       <c r="C647" t="n">
         <v>1</v>
       </c>
+      <c r="D647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="n">
@@ -7299,6 +7950,7 @@
       <c r="C648" t="n">
         <v>0</v>
       </c>
+      <c r="D648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="n">
@@ -7308,6 +7960,7 @@
       <c r="C649" t="n">
         <v>0</v>
       </c>
+      <c r="D649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="n">
@@ -7317,6 +7970,7 @@
       <c r="C650" t="n">
         <v>0</v>
       </c>
+      <c r="D650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="n">
@@ -7326,6 +7980,7 @@
       <c r="C651" t="n">
         <v>0</v>
       </c>
+      <c r="D651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="n">
@@ -7335,6 +7990,7 @@
       <c r="C652" t="n">
         <v>0</v>
       </c>
+      <c r="D652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="n">
@@ -7348,6 +8004,7 @@
       <c r="C653" t="n">
         <v>1</v>
       </c>
+      <c r="D653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="n">
@@ -7361,6 +8018,7 @@
       <c r="C654" t="n">
         <v>1</v>
       </c>
+      <c r="D654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="n">
@@ -7370,6 +8028,7 @@
       <c r="C655" t="n">
         <v>0</v>
       </c>
+      <c r="D655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="n">
@@ -7379,6 +8038,7 @@
       <c r="C656" t="n">
         <v>0</v>
       </c>
+      <c r="D656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="n">
@@ -7388,6 +8048,7 @@
       <c r="C657" t="n">
         <v>0</v>
       </c>
+      <c r="D657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="n">
@@ -7397,6 +8058,7 @@
       <c r="C658" t="n">
         <v>0</v>
       </c>
+      <c r="D658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="n">
@@ -7406,6 +8068,7 @@
       <c r="C659" t="n">
         <v>0</v>
       </c>
+      <c r="D659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="n">
@@ -7419,6 +8082,7 @@
       <c r="C660" t="n">
         <v>1</v>
       </c>
+      <c r="D660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="n">
@@ -7432,6 +8096,7 @@
       <c r="C661" t="n">
         <v>1</v>
       </c>
+      <c r="D661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="n">
@@ -7441,6 +8106,7 @@
       <c r="C662" t="n">
         <v>0</v>
       </c>
+      <c r="D662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="n">
@@ -7450,6 +8116,7 @@
       <c r="C663" t="n">
         <v>0</v>
       </c>
+      <c r="D663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="n">
@@ -7459,6 +8126,7 @@
       <c r="C664" t="n">
         <v>0</v>
       </c>
+      <c r="D664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="n">
@@ -7468,6 +8136,7 @@
       <c r="C665" t="n">
         <v>0</v>
       </c>
+      <c r="D665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="n">
@@ -7477,6 +8146,7 @@
       <c r="C666" t="n">
         <v>0</v>
       </c>
+      <c r="D666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="n">
@@ -7490,6 +8160,7 @@
       <c r="C667" t="n">
         <v>1</v>
       </c>
+      <c r="D667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="n">
@@ -7503,6 +8174,7 @@
       <c r="C668" t="n">
         <v>1</v>
       </c>
+      <c r="D668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="n">
@@ -7512,6 +8184,7 @@
       <c r="C669" t="n">
         <v>0</v>
       </c>
+      <c r="D669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="n">
@@ -7521,6 +8194,7 @@
       <c r="C670" t="n">
         <v>0</v>
       </c>
+      <c r="D670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="n">
@@ -7530,6 +8204,7 @@
       <c r="C671" t="n">
         <v>0</v>
       </c>
+      <c r="D671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="n">
@@ -7539,6 +8214,7 @@
       <c r="C672" t="n">
         <v>0</v>
       </c>
+      <c r="D672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="n">
@@ -7548,6 +8224,7 @@
       <c r="C673" t="n">
         <v>0</v>
       </c>
+      <c r="D673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="n">
@@ -7561,6 +8238,7 @@
       <c r="C674" t="n">
         <v>1</v>
       </c>
+      <c r="D674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="n">
@@ -7574,6 +8252,7 @@
       <c r="C675" t="n">
         <v>1</v>
       </c>
+      <c r="D675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="n">
@@ -7583,6 +8262,7 @@
       <c r="C676" t="n">
         <v>0</v>
       </c>
+      <c r="D676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="n">
@@ -7592,6 +8272,7 @@
       <c r="C677" t="n">
         <v>0</v>
       </c>
+      <c r="D677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="n">
@@ -7601,6 +8282,7 @@
       <c r="C678" t="n">
         <v>0</v>
       </c>
+      <c r="D678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="n">
@@ -7610,6 +8292,7 @@
       <c r="C679" t="n">
         <v>0</v>
       </c>
+      <c r="D679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="n">
@@ -7619,6 +8302,7 @@
       <c r="C680" t="n">
         <v>0</v>
       </c>
+      <c r="D680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="n">
@@ -7632,6 +8316,7 @@
       <c r="C681" t="n">
         <v>1</v>
       </c>
+      <c r="D681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="n">
@@ -7645,6 +8330,7 @@
       <c r="C682" t="n">
         <v>1</v>
       </c>
+      <c r="D682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="n">
@@ -7654,6 +8340,7 @@
       <c r="C683" t="n">
         <v>0</v>
       </c>
+      <c r="D683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="n">
@@ -7663,6 +8350,7 @@
       <c r="C684" t="n">
         <v>0</v>
       </c>
+      <c r="D684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="n">
@@ -7672,6 +8360,7 @@
       <c r="C685" t="n">
         <v>0</v>
       </c>
+      <c r="D685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="n">
@@ -7681,6 +8370,7 @@
       <c r="C686" t="n">
         <v>0</v>
       </c>
+      <c r="D686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="n">
@@ -7690,6 +8380,7 @@
       <c r="C687" t="n">
         <v>0</v>
       </c>
+      <c r="D687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="n">
@@ -7703,6 +8394,7 @@
       <c r="C688" t="n">
         <v>1</v>
       </c>
+      <c r="D688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="n">
@@ -7716,6 +8408,7 @@
       <c r="C689" t="n">
         <v>1</v>
       </c>
+      <c r="D689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="n">
@@ -7725,6 +8418,7 @@
       <c r="C690" t="n">
         <v>0</v>
       </c>
+      <c r="D690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="n">
@@ -7734,6 +8428,7 @@
       <c r="C691" t="n">
         <v>0</v>
       </c>
+      <c r="D691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="n">
@@ -7743,6 +8438,7 @@
       <c r="C692" t="n">
         <v>0</v>
       </c>
+      <c r="D692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="n">
@@ -7752,6 +8448,7 @@
       <c r="C693" t="n">
         <v>0</v>
       </c>
+      <c r="D693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="n">
@@ -7761,6 +8458,7 @@
       <c r="C694" t="n">
         <v>0</v>
       </c>
+      <c r="D694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="n">
@@ -7774,6 +8472,7 @@
       <c r="C695" t="n">
         <v>1</v>
       </c>
+      <c r="D695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="n">
@@ -7787,6 +8486,7 @@
       <c r="C696" t="n">
         <v>1</v>
       </c>
+      <c r="D696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="n">
@@ -7796,6 +8496,7 @@
       <c r="C697" t="n">
         <v>0</v>
       </c>
+      <c r="D697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="n">
@@ -7805,6 +8506,7 @@
       <c r="C698" t="n">
         <v>0</v>
       </c>
+      <c r="D698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="n">
@@ -7814,6 +8516,7 @@
       <c r="C699" t="n">
         <v>0</v>
       </c>
+      <c r="D699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="n">
@@ -7823,6 +8526,7 @@
       <c r="C700" t="n">
         <v>0</v>
       </c>
+      <c r="D700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="n">
@@ -7832,6 +8536,7 @@
       <c r="C701" t="n">
         <v>0</v>
       </c>
+      <c r="D701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="2" t="n">
@@ -7845,6 +8550,7 @@
       <c r="C702" t="n">
         <v>1</v>
       </c>
+      <c r="D702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="n">
@@ -7858,6 +8564,7 @@
       <c r="C703" t="n">
         <v>1</v>
       </c>
+      <c r="D703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="n">
@@ -7867,6 +8574,7 @@
       <c r="C704" t="n">
         <v>0</v>
       </c>
+      <c r="D704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" s="2" t="n">
@@ -7876,6 +8584,7 @@
       <c r="C705" t="n">
         <v>0</v>
       </c>
+      <c r="D705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="n">
@@ -7885,6 +8594,7 @@
       <c r="C706" t="n">
         <v>0</v>
       </c>
+      <c r="D706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="n">
@@ -7894,6 +8604,7 @@
       <c r="C707" t="n">
         <v>0</v>
       </c>
+      <c r="D707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="n">
@@ -7903,6 +8614,7 @@
       <c r="C708" t="n">
         <v>0</v>
       </c>
+      <c r="D708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="n">
@@ -7916,6 +8628,7 @@
       <c r="C709" t="n">
         <v>1</v>
       </c>
+      <c r="D709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="n">
@@ -7929,6 +8642,7 @@
       <c r="C710" t="n">
         <v>1</v>
       </c>
+      <c r="D710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="n">
@@ -7938,6 +8652,7 @@
       <c r="C711" t="n">
         <v>0</v>
       </c>
+      <c r="D711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="n">
@@ -7947,6 +8662,7 @@
       <c r="C712" t="n">
         <v>0</v>
       </c>
+      <c r="D712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="2" t="n">
@@ -7956,6 +8672,7 @@
       <c r="C713" t="n">
         <v>0</v>
       </c>
+      <c r="D713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="n">
@@ -7965,6 +8682,7 @@
       <c r="C714" t="n">
         <v>0</v>
       </c>
+      <c r="D714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="n">
@@ -7974,6 +8692,7 @@
       <c r="C715" t="n">
         <v>0</v>
       </c>
+      <c r="D715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" s="2" t="n">
@@ -7987,6 +8706,7 @@
       <c r="C716" t="n">
         <v>1</v>
       </c>
+      <c r="D716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="n">
@@ -8000,6 +8720,7 @@
       <c r="C717" t="n">
         <v>1</v>
       </c>
+      <c r="D717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" s="2" t="n">
@@ -8009,6 +8730,7 @@
       <c r="C718" t="n">
         <v>0</v>
       </c>
+      <c r="D718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="2" t="n">
@@ -8018,6 +8740,7 @@
       <c r="C719" t="n">
         <v>0</v>
       </c>
+      <c r="D719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" s="2" t="n">
@@ -8027,6 +8750,7 @@
       <c r="C720" t="n">
         <v>0</v>
       </c>
+      <c r="D720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="2" t="n">
@@ -8036,6 +8760,7 @@
       <c r="C721" t="n">
         <v>0</v>
       </c>
+      <c r="D721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="2" t="n">
@@ -8045,6 +8770,7 @@
       <c r="C722" t="n">
         <v>0</v>
       </c>
+      <c r="D722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" s="2" t="n">
@@ -8058,6 +8784,7 @@
       <c r="C723" t="n">
         <v>1</v>
       </c>
+      <c r="D723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" s="2" t="n">
@@ -8071,6 +8798,7 @@
       <c r="C724" t="n">
         <v>1</v>
       </c>
+      <c r="D724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" s="2" t="n">
@@ -8084,6 +8812,7 @@
       <c r="C725" t="n">
         <v>1</v>
       </c>
+      <c r="D725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" s="2" t="n">
@@ -8097,6 +8826,7 @@
       <c r="C726" t="n">
         <v>1</v>
       </c>
+      <c r="D726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="2" t="n">
@@ -8110,6 +8840,7 @@
       <c r="C727" t="n">
         <v>1</v>
       </c>
+      <c r="D727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" s="2" t="n">
@@ -8123,6 +8854,7 @@
       <c r="C728" t="n">
         <v>1</v>
       </c>
+      <c r="D728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="2" t="n">
@@ -8136,6 +8868,7 @@
       <c r="C729" t="n">
         <v>1</v>
       </c>
+      <c r="D729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" s="2" t="n">
@@ -8149,6 +8882,7 @@
       <c r="C730" t="n">
         <v>1</v>
       </c>
+      <c r="D730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" s="2" t="n">
@@ -8162,6 +8896,7 @@
       <c r="C731" t="n">
         <v>1</v>
       </c>
+      <c r="D731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" s="2" t="n">
@@ -8175,6 +8910,7 @@
       <c r="C732" t="n">
         <v>1</v>
       </c>
+      <c r="D732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="2" t="n">
@@ -8184,6 +8920,7 @@
       <c r="C733" t="n">
         <v>0</v>
       </c>
+      <c r="D733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="2" t="n">
@@ -8193,6 +8930,7 @@
       <c r="C734" t="n">
         <v>0</v>
       </c>
+      <c r="D734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="2" t="n">
@@ -8202,6 +8940,7 @@
       <c r="C735" t="n">
         <v>0</v>
       </c>
+      <c r="D735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="2" t="n">
@@ -8211,6 +8950,7 @@
       <c r="C736" t="n">
         <v>0</v>
       </c>
+      <c r="D736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="2" t="n">
@@ -8224,6 +8964,7 @@
       <c r="C737" t="n">
         <v>1</v>
       </c>
+      <c r="D737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="2" t="n">
@@ -8237,6 +8978,7 @@
       <c r="C738" t="n">
         <v>1</v>
       </c>
+      <c r="D738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="2" t="n">
@@ -8246,6 +8988,7 @@
       <c r="C739" t="n">
         <v>0</v>
       </c>
+      <c r="D739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="2" t="n">
@@ -8255,6 +8998,7 @@
       <c r="C740" t="n">
         <v>0</v>
       </c>
+      <c r="D740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="2" t="n">
@@ -8264,6 +9008,7 @@
       <c r="C741" t="n">
         <v>0</v>
       </c>
+      <c r="D741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" s="2" t="n">
@@ -8273,6 +9018,7 @@
       <c r="C742" t="n">
         <v>0</v>
       </c>
+      <c r="D742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" s="2" t="n">
@@ -8282,6 +9028,7 @@
       <c r="C743" t="n">
         <v>0</v>
       </c>
+      <c r="D743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" s="2" t="n">
@@ -8295,6 +9042,7 @@
       <c r="C744" t="n">
         <v>1</v>
       </c>
+      <c r="D744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" s="2" t="n">
@@ -8308,6 +9056,7 @@
       <c r="C745" t="n">
         <v>1</v>
       </c>
+      <c r="D745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" s="2" t="n">
@@ -8317,6 +9066,7 @@
       <c r="C746" t="n">
         <v>0</v>
       </c>
+      <c r="D746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" s="2" t="n">
@@ -8326,6 +9076,7 @@
       <c r="C747" t="n">
         <v>0</v>
       </c>
+      <c r="D747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" s="2" t="n">
@@ -8335,6 +9086,7 @@
       <c r="C748" t="n">
         <v>0</v>
       </c>
+      <c r="D748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" s="2" t="n">
@@ -8344,6 +9096,7 @@
       <c r="C749" t="n">
         <v>0</v>
       </c>
+      <c r="D749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" s="2" t="n">
@@ -8353,6 +9106,7 @@
       <c r="C750" t="n">
         <v>0</v>
       </c>
+      <c r="D750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" s="2" t="n">
@@ -8366,6 +9120,7 @@
       <c r="C751" t="n">
         <v>1</v>
       </c>
+      <c r="D751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" s="2" t="n">
@@ -8379,6 +9134,7 @@
       <c r="C752" t="n">
         <v>1</v>
       </c>
+      <c r="D752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" s="2" t="n">
@@ -8388,6 +9144,7 @@
       <c r="C753" t="n">
         <v>0</v>
       </c>
+      <c r="D753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" s="2" t="n">
@@ -8397,6 +9154,7 @@
       <c r="C754" t="n">
         <v>0</v>
       </c>
+      <c r="D754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" s="2" t="n">
@@ -8406,6 +9164,7 @@
       <c r="C755" t="n">
         <v>0</v>
       </c>
+      <c r="D755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" s="2" t="n">
@@ -8415,6 +9174,7 @@
       <c r="C756" t="n">
         <v>0</v>
       </c>
+      <c r="D756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" s="2" t="n">
@@ -8424,6 +9184,7 @@
       <c r="C757" t="n">
         <v>0</v>
       </c>
+      <c r="D757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" s="2" t="n">
@@ -8437,6 +9198,7 @@
       <c r="C758" t="n">
         <v>1</v>
       </c>
+      <c r="D758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" s="2" t="n">
@@ -8450,6 +9212,7 @@
       <c r="C759" t="n">
         <v>1</v>
       </c>
+      <c r="D759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" s="2" t="n">
@@ -8459,6 +9222,7 @@
       <c r="C760" t="n">
         <v>0</v>
       </c>
+      <c r="D760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" s="2" t="n">
@@ -8468,6 +9232,7 @@
       <c r="C761" t="n">
         <v>0</v>
       </c>
+      <c r="D761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" s="2" t="n">
@@ -8477,6 +9242,7 @@
       <c r="C762" t="n">
         <v>0</v>
       </c>
+      <c r="D762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" s="2" t="n">
@@ -8486,6 +9252,7 @@
       <c r="C763" t="n">
         <v>0</v>
       </c>
+      <c r="D763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" s="2" t="n">
@@ -8495,6 +9262,7 @@
       <c r="C764" t="n">
         <v>0</v>
       </c>
+      <c r="D764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" s="2" t="n">
@@ -8508,6 +9276,7 @@
       <c r="C765" t="n">
         <v>1</v>
       </c>
+      <c r="D765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" s="2" t="n">
@@ -8521,6 +9290,7 @@
       <c r="C766" t="n">
         <v>1</v>
       </c>
+      <c r="D766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" s="2" t="n">
@@ -8530,6 +9300,7 @@
       <c r="C767" t="n">
         <v>0</v>
       </c>
+      <c r="D767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" s="2" t="n">
@@ -8539,6 +9310,7 @@
       <c r="C768" t="n">
         <v>0</v>
       </c>
+      <c r="D768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" s="2" t="n">
@@ -8548,6 +9320,7 @@
       <c r="C769" t="n">
         <v>0</v>
       </c>
+      <c r="D769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" s="2" t="n">
@@ -8561,6 +9334,7 @@
       <c r="C770" t="n">
         <v>1</v>
       </c>
+      <c r="D770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" s="2" t="n">
@@ -8574,6 +9348,7 @@
       <c r="C771" t="n">
         <v>1</v>
       </c>
+      <c r="D771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" s="2" t="n">
@@ -8587,6 +9362,7 @@
       <c r="C772" t="n">
         <v>1</v>
       </c>
+      <c r="D772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" s="2" t="n">
@@ -8600,6 +9376,7 @@
       <c r="C773" t="n">
         <v>1</v>
       </c>
+      <c r="D773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" s="2" t="n">
@@ -8609,6 +9386,7 @@
       <c r="C774" t="n">
         <v>0</v>
       </c>
+      <c r="D774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" s="2" t="n">
@@ -8618,6 +9396,7 @@
       <c r="C775" t="n">
         <v>0</v>
       </c>
+      <c r="D775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" s="2" t="n">
@@ -8631,6 +9410,7 @@
       <c r="C776" t="n">
         <v>1</v>
       </c>
+      <c r="D776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" s="2" t="n">
@@ -8640,6 +9420,7 @@
       <c r="C777" t="n">
         <v>0</v>
       </c>
+      <c r="D777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" s="2" t="n">
@@ -8649,6 +9430,7 @@
       <c r="C778" t="n">
         <v>0</v>
       </c>
+      <c r="D778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" s="2" t="n">
@@ -8662,6 +9444,7 @@
       <c r="C779" t="n">
         <v>1</v>
       </c>
+      <c r="D779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" s="2" t="n">
@@ -8675,6 +9458,7 @@
       <c r="C780" t="n">
         <v>1</v>
       </c>
+      <c r="D780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" s="2" t="n">
@@ -8684,6 +9468,7 @@
       <c r="C781" t="n">
         <v>0</v>
       </c>
+      <c r="D781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" s="2" t="n">
@@ -8693,6 +9478,7 @@
       <c r="C782" t="n">
         <v>0</v>
       </c>
+      <c r="D782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" s="2" t="n">
@@ -8702,6 +9488,7 @@
       <c r="C783" t="n">
         <v>0</v>
       </c>
+      <c r="D783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" s="2" t="n">
@@ -8711,6 +9498,7 @@
       <c r="C784" t="n">
         <v>0</v>
       </c>
+      <c r="D784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" s="2" t="n">
@@ -8720,6 +9508,7 @@
       <c r="C785" t="n">
         <v>0</v>
       </c>
+      <c r="D785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" s="2" t="n">
@@ -8733,6 +9522,7 @@
       <c r="C786" t="n">
         <v>1</v>
       </c>
+      <c r="D786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" s="2" t="n">
@@ -8746,6 +9536,7 @@
       <c r="C787" t="n">
         <v>1</v>
       </c>
+      <c r="D787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" s="2" t="n">
@@ -8755,6 +9546,7 @@
       <c r="C788" t="n">
         <v>0</v>
       </c>
+      <c r="D788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" s="2" t="n">
@@ -8764,6 +9556,7 @@
       <c r="C789" t="n">
         <v>0</v>
       </c>
+      <c r="D789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" s="2" t="n">
@@ -8773,6 +9566,7 @@
       <c r="C790" t="n">
         <v>0</v>
       </c>
+      <c r="D790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" s="2" t="n">
@@ -8782,6 +9576,7 @@
       <c r="C791" t="n">
         <v>0</v>
       </c>
+      <c r="D791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" s="2" t="n">
@@ -8791,6 +9586,7 @@
       <c r="C792" t="n">
         <v>0</v>
       </c>
+      <c r="D792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" s="2" t="n">
@@ -8804,6 +9600,7 @@
       <c r="C793" t="n">
         <v>1</v>
       </c>
+      <c r="D793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" s="2" t="n">
@@ -8817,6 +9614,7 @@
       <c r="C794" t="n">
         <v>1</v>
       </c>
+      <c r="D794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" s="2" t="n">
@@ -8826,6 +9624,7 @@
       <c r="C795" t="n">
         <v>0</v>
       </c>
+      <c r="D795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" s="2" t="n">
@@ -8835,6 +9634,7 @@
       <c r="C796" t="n">
         <v>0</v>
       </c>
+      <c r="D796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" s="2" t="n">
@@ -8844,6 +9644,7 @@
       <c r="C797" t="n">
         <v>0</v>
       </c>
+      <c r="D797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" s="2" t="n">
@@ -8853,6 +9654,7 @@
       <c r="C798" t="n">
         <v>0</v>
       </c>
+      <c r="D798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" s="2" t="n">
@@ -8862,6 +9664,7 @@
       <c r="C799" t="n">
         <v>0</v>
       </c>
+      <c r="D799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" s="2" t="n">
@@ -8875,6 +9678,7 @@
       <c r="C800" t="n">
         <v>1</v>
       </c>
+      <c r="D800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" s="2" t="n">
@@ -8888,6 +9692,7 @@
       <c r="C801" t="n">
         <v>1</v>
       </c>
+      <c r="D801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" s="2" t="n">
@@ -8901,6 +9706,7 @@
       <c r="C802" t="n">
         <v>1</v>
       </c>
+      <c r="D802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" s="2" t="n">
@@ -8914,6 +9720,7 @@
       <c r="C803" t="n">
         <v>1</v>
       </c>
+      <c r="D803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" s="2" t="n">
@@ -8923,6 +9730,7 @@
       <c r="C804" t="n">
         <v>0</v>
       </c>
+      <c r="D804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" s="2" t="n">
@@ -8932,6 +9740,7 @@
       <c r="C805" t="n">
         <v>0</v>
       </c>
+      <c r="D805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" s="2" t="n">
@@ -8941,6 +9750,7 @@
       <c r="C806" t="n">
         <v>0</v>
       </c>
+      <c r="D806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" s="2" t="n">
@@ -8954,6 +9764,7 @@
       <c r="C807" t="n">
         <v>1</v>
       </c>
+      <c r="D807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" s="2" t="n">
@@ -8967,6 +9778,7 @@
       <c r="C808" t="n">
         <v>1</v>
       </c>
+      <c r="D808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" s="2" t="n">
@@ -8976,6 +9788,7 @@
       <c r="C809" t="n">
         <v>0</v>
       </c>
+      <c r="D809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" s="2" t="n">
@@ -8985,6 +9798,7 @@
       <c r="C810" t="n">
         <v>0</v>
       </c>
+      <c r="D810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" s="2" t="n">
@@ -8994,6 +9808,7 @@
       <c r="C811" t="n">
         <v>0</v>
       </c>
+      <c r="D811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" s="2" t="n">
@@ -9003,6 +9818,7 @@
       <c r="C812" t="n">
         <v>0</v>
       </c>
+      <c r="D812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" s="2" t="n">
@@ -9012,6 +9828,7 @@
       <c r="C813" t="n">
         <v>0</v>
       </c>
+      <c r="D813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" s="2" t="n">
@@ -9025,6 +9842,7 @@
       <c r="C814" t="n">
         <v>1</v>
       </c>
+      <c r="D814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" s="2" t="n">
@@ -9038,6 +9856,7 @@
       <c r="C815" t="n">
         <v>1</v>
       </c>
+      <c r="D815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" s="2" t="n">
@@ -9047,6 +9866,7 @@
       <c r="C816" t="n">
         <v>0</v>
       </c>
+      <c r="D816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" s="2" t="n">
@@ -9056,6 +9876,7 @@
       <c r="C817" t="n">
         <v>0</v>
       </c>
+      <c r="D817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" s="2" t="n">
@@ -9065,6 +9886,7 @@
       <c r="C818" t="n">
         <v>0</v>
       </c>
+      <c r="D818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" s="2" t="n">
@@ -9074,6 +9896,7 @@
       <c r="C819" t="n">
         <v>0</v>
       </c>
+      <c r="D819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" s="2" t="n">
@@ -9087,6 +9910,7 @@
       <c r="C820" t="n">
         <v>1</v>
       </c>
+      <c r="D820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" s="2" t="n">
@@ -9100,6 +9924,7 @@
       <c r="C821" t="n">
         <v>1</v>
       </c>
+      <c r="D821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" s="2" t="n">
@@ -9113,6 +9938,7 @@
       <c r="C822" t="n">
         <v>1</v>
       </c>
+      <c r="D822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" s="2" t="n">
@@ -9122,6 +9948,7 @@
       <c r="C823" t="n">
         <v>0</v>
       </c>
+      <c r="D823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" s="2" t="n">
@@ -9131,6 +9958,7 @@
       <c r="C824" t="n">
         <v>0</v>
       </c>
+      <c r="D824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" s="2" t="n">
@@ -9140,6 +9968,7 @@
       <c r="C825" t="n">
         <v>0</v>
       </c>
+      <c r="D825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" s="2" t="n">
@@ -9149,6 +9978,7 @@
       <c r="C826" t="n">
         <v>0</v>
       </c>
+      <c r="D826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" s="2" t="n">
@@ -9158,6 +9988,7 @@
       <c r="C827" t="n">
         <v>0</v>
       </c>
+      <c r="D827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" s="2" t="n">
@@ -9171,6 +10002,7 @@
       <c r="C828" t="n">
         <v>1</v>
       </c>
+      <c r="D828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" s="2" t="n">
@@ -9184,6 +10016,7 @@
       <c r="C829" t="n">
         <v>1</v>
       </c>
+      <c r="D829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" s="2" t="n">
@@ -9197,6 +10030,7 @@
       <c r="C830" t="n">
         <v>1</v>
       </c>
+      <c r="D830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" s="2" t="n">
@@ -9210,6 +10044,7 @@
       <c r="C831" t="n">
         <v>1</v>
       </c>
+      <c r="D831" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" s="2" t="n">
@@ -9223,6 +10058,7 @@
       <c r="C832" t="n">
         <v>1</v>
       </c>
+      <c r="D832" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" s="2" t="n">
@@ -9236,6 +10072,7 @@
       <c r="C833" t="n">
         <v>1</v>
       </c>
+      <c r="D833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" s="2" t="n">
@@ -9249,6 +10086,7 @@
       <c r="C834" t="n">
         <v>1</v>
       </c>
+      <c r="D834" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" s="2" t="n">
@@ -9262,6 +10100,7 @@
       <c r="C835" t="n">
         <v>1</v>
       </c>
+      <c r="D835" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" s="2" t="n">
@@ -9275,6 +10114,7 @@
       <c r="C836" t="n">
         <v>1</v>
       </c>
+      <c r="D836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" s="2" t="n">
@@ -9288,6 +10128,7 @@
       <c r="C837" t="n">
         <v>1</v>
       </c>
+      <c r="D837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" s="2" t="n">
@@ -9297,6 +10138,7 @@
       <c r="C838" t="n">
         <v>0</v>
       </c>
+      <c r="D838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" s="2" t="n">
@@ -9306,6 +10148,7 @@
       <c r="C839" t="n">
         <v>0</v>
       </c>
+      <c r="D839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" s="2" t="n">
@@ -9315,6 +10158,7 @@
       <c r="C840" t="n">
         <v>0</v>
       </c>
+      <c r="D840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" s="2" t="n">
@@ -9324,6 +10168,7 @@
       <c r="C841" t="n">
         <v>0</v>
       </c>
+      <c r="D841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" s="2" t="n">
@@ -9337,6 +10182,7 @@
       <c r="C842" t="n">
         <v>1</v>
       </c>
+      <c r="D842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" s="2" t="n">
@@ -9350,6 +10196,7 @@
       <c r="C843" t="n">
         <v>1</v>
       </c>
+      <c r="D843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" s="2" t="n">
@@ -9359,6 +10206,7 @@
       <c r="C844" t="n">
         <v>0</v>
       </c>
+      <c r="D844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" s="2" t="n">
@@ -9368,6 +10216,7 @@
       <c r="C845" t="n">
         <v>0</v>
       </c>
+      <c r="D845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" s="2" t="n">
@@ -9377,6 +10226,7 @@
       <c r="C846" t="n">
         <v>0</v>
       </c>
+      <c r="D846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" s="2" t="n">
@@ -9386,6 +10236,7 @@
       <c r="C847" t="n">
         <v>0</v>
       </c>
+      <c r="D847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" s="2" t="n">
@@ -9395,6 +10246,7 @@
       <c r="C848" t="n">
         <v>0</v>
       </c>
+      <c r="D848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" s="2" t="n">
@@ -9408,6 +10260,7 @@
       <c r="C849" t="n">
         <v>1</v>
       </c>
+      <c r="D849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" s="2" t="n">
@@ -9421,6 +10274,7 @@
       <c r="C850" t="n">
         <v>1</v>
       </c>
+      <c r="D850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" s="2" t="n">
@@ -9430,6 +10284,7 @@
       <c r="C851" t="n">
         <v>0</v>
       </c>
+      <c r="D851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" s="2" t="n">
@@ -9439,6 +10294,7 @@
       <c r="C852" t="n">
         <v>0</v>
       </c>
+      <c r="D852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" s="2" t="n">
@@ -9452,6 +10308,7 @@
       <c r="C853" t="n">
         <v>1</v>
       </c>
+      <c r="D853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" s="2" t="n">
@@ -9461,6 +10318,7 @@
       <c r="C854" t="n">
         <v>0</v>
       </c>
+      <c r="D854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" s="2" t="n">
@@ -9470,6 +10328,7 @@
       <c r="C855" t="n">
         <v>0</v>
       </c>
+      <c r="D855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" s="2" t="n">
@@ -9483,6 +10342,7 @@
       <c r="C856" t="n">
         <v>1</v>
       </c>
+      <c r="D856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" s="2" t="n">
@@ -9496,6 +10356,7 @@
       <c r="C857" t="n">
         <v>1</v>
       </c>
+      <c r="D857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" s="2" t="n">
@@ -9505,6 +10366,7 @@
       <c r="C858" t="n">
         <v>0</v>
       </c>
+      <c r="D858" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" s="2" t="n">
@@ -9514,6 +10376,7 @@
       <c r="C859" t="n">
         <v>0</v>
       </c>
+      <c r="D859" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" s="2" t="n">
@@ -9523,6 +10386,7 @@
       <c r="C860" t="n">
         <v>0</v>
       </c>
+      <c r="D860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" s="2" t="n">
@@ -9536,6 +10400,7 @@
       <c r="C861" t="n">
         <v>1</v>
       </c>
+      <c r="D861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" s="2" t="n">
@@ -9549,6 +10414,7 @@
       <c r="C862" t="n">
         <v>1</v>
       </c>
+      <c r="D862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" s="2" t="n">
@@ -9562,6 +10428,7 @@
       <c r="C863" t="n">
         <v>1</v>
       </c>
+      <c r="D863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" s="2" t="n">
@@ -9575,6 +10442,7 @@
       <c r="C864" t="n">
         <v>1</v>
       </c>
+      <c r="D864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" s="2" t="n">
@@ -9584,6 +10452,7 @@
       <c r="C865" t="n">
         <v>0</v>
       </c>
+      <c r="D865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" s="2" t="n">
@@ -9593,6 +10462,7 @@
       <c r="C866" t="n">
         <v>0</v>
       </c>
+      <c r="D866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" s="2" t="n">
@@ -9602,6 +10472,7 @@
       <c r="C867" t="n">
         <v>0</v>
       </c>
+      <c r="D867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" s="2" t="n">
@@ -9611,6 +10482,7 @@
       <c r="C868" t="n">
         <v>0</v>
       </c>
+      <c r="D868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" s="2" t="n">
@@ -9620,6 +10492,7 @@
       <c r="C869" t="n">
         <v>0</v>
       </c>
+      <c r="D869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" s="2" t="n">
@@ -9633,6 +10506,7 @@
       <c r="C870" t="n">
         <v>1</v>
       </c>
+      <c r="D870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" s="2" t="n">
@@ -9646,6 +10520,7 @@
       <c r="C871" t="n">
         <v>1</v>
       </c>
+      <c r="D871" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" s="2" t="n">
@@ -9655,6 +10530,7 @@
       <c r="C872" t="n">
         <v>0</v>
       </c>
+      <c r="D872" t="inlineStr"/>
     </row>
     <row r="873">
       <c r="A873" s="2" t="n">
@@ -9664,6 +10540,7 @@
       <c r="C873" t="n">
         <v>0</v>
       </c>
+      <c r="D873" t="inlineStr"/>
     </row>
     <row r="874">
       <c r="A874" s="2" t="n">
@@ -9673,6 +10550,7 @@
       <c r="C874" t="n">
         <v>0</v>
       </c>
+      <c r="D874" t="inlineStr"/>
     </row>
     <row r="875">
       <c r="A875" s="2" t="n">
@@ -9686,6 +10564,7 @@
       <c r="C875" t="n">
         <v>1</v>
       </c>
+      <c r="D875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" s="2" t="n">
@@ -9699,6 +10578,7 @@
       <c r="C876" t="n">
         <v>1</v>
       </c>
+      <c r="D876" t="inlineStr"/>
     </row>
     <row r="877">
       <c r="A877" s="2" t="n">
@@ -9712,6 +10592,7 @@
       <c r="C877" t="n">
         <v>1</v>
       </c>
+      <c r="D877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" s="2" t="n">
@@ -9725,6 +10606,7 @@
       <c r="C878" t="n">
         <v>1</v>
       </c>
+      <c r="D878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" s="2" t="n">
@@ -9734,6 +10616,7 @@
       <c r="C879" t="n">
         <v>0</v>
       </c>
+      <c r="D879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" s="2" t="n">
@@ -9743,6 +10626,7 @@
       <c r="C880" t="n">
         <v>0</v>
       </c>
+      <c r="D880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" s="2" t="n">
@@ -9752,6 +10636,7 @@
       <c r="C881" t="n">
         <v>0</v>
       </c>
+      <c r="D881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" s="2" t="n">
@@ -9761,6 +10646,7 @@
       <c r="C882" t="n">
         <v>0</v>
       </c>
+      <c r="D882" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" s="2" t="n">
@@ -9770,6 +10656,7 @@
       <c r="C883" t="n">
         <v>0</v>
       </c>
+      <c r="D883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" s="2" t="n">
@@ -9783,6 +10670,7 @@
       <c r="C884" t="n">
         <v>1</v>
       </c>
+      <c r="D884" t="inlineStr"/>
     </row>
     <row r="885">
       <c r="A885" s="2" t="n">
@@ -9796,6 +10684,7 @@
       <c r="C885" t="n">
         <v>1</v>
       </c>
+      <c r="D885" t="inlineStr"/>
     </row>
     <row r="886">
       <c r="A886" s="2" t="n">
@@ -9805,6 +10694,7 @@
       <c r="C886" t="n">
         <v>0</v>
       </c>
+      <c r="D886" t="inlineStr"/>
     </row>
     <row r="887">
       <c r="A887" s="2" t="n">
@@ -9814,6 +10704,7 @@
       <c r="C887" t="n">
         <v>0</v>
       </c>
+      <c r="D887" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" s="2" t="n">
@@ -9823,6 +10714,7 @@
       <c r="C888" t="n">
         <v>0</v>
       </c>
+      <c r="D888" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" s="2" t="n">
@@ -9832,6 +10724,7 @@
       <c r="C889" t="n">
         <v>0</v>
       </c>
+      <c r="D889" t="inlineStr"/>
     </row>
     <row r="890">
       <c r="A890" s="2" t="n">
@@ -9841,6 +10734,7 @@
       <c r="C890" t="n">
         <v>0</v>
       </c>
+      <c r="D890" t="inlineStr"/>
     </row>
     <row r="891">
       <c r="A891" s="2" t="n">
@@ -9854,6 +10748,7 @@
       <c r="C891" t="n">
         <v>1</v>
       </c>
+      <c r="D891" t="inlineStr"/>
     </row>
     <row r="892">
       <c r="A892" s="2" t="n">
@@ -9867,6 +10762,7 @@
       <c r="C892" t="n">
         <v>1</v>
       </c>
+      <c r="D892" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" s="2" t="n">
@@ -9876,6 +10772,7 @@
       <c r="C893" t="n">
         <v>0</v>
       </c>
+      <c r="D893" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" s="2" t="n">
@@ -9885,6 +10782,7 @@
       <c r="C894" t="n">
         <v>0</v>
       </c>
+      <c r="D894" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" s="2" t="n">
@@ -9894,6 +10792,7 @@
       <c r="C895" t="n">
         <v>0</v>
       </c>
+      <c r="D895" t="inlineStr"/>
     </row>
     <row r="896">
       <c r="A896" s="2" t="n">
@@ -9903,6 +10802,7 @@
       <c r="C896" t="n">
         <v>0</v>
       </c>
+      <c r="D896" t="inlineStr"/>
     </row>
     <row r="897">
       <c r="A897" s="2" t="n">
@@ -9912,6 +10812,7 @@
       <c r="C897" t="n">
         <v>0</v>
       </c>
+      <c r="D897" t="inlineStr"/>
     </row>
     <row r="898">
       <c r="A898" s="2" t="n">
@@ -9925,6 +10826,7 @@
       <c r="C898" t="n">
         <v>1</v>
       </c>
+      <c r="D898" t="inlineStr"/>
     </row>
     <row r="899">
       <c r="A899" s="2" t="n">
@@ -9938,6 +10840,7 @@
       <c r="C899" t="n">
         <v>1</v>
       </c>
+      <c r="D899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" s="2" t="n">
@@ -9951,6 +10854,7 @@
       <c r="C900" t="n">
         <v>1</v>
       </c>
+      <c r="D900" t="inlineStr"/>
     </row>
     <row r="901">
       <c r="A901" s="2" t="n">
@@ -9964,6 +10868,7 @@
       <c r="C901" t="n">
         <v>1</v>
       </c>
+      <c r="D901" t="inlineStr"/>
     </row>
     <row r="902">
       <c r="A902" s="2" t="n">
@@ -9973,6 +10878,7 @@
       <c r="C902" t="n">
         <v>0</v>
       </c>
+      <c r="D902" t="inlineStr"/>
     </row>
     <row r="903">
       <c r="A903" s="2" t="n">
@@ -9982,6 +10888,7 @@
       <c r="C903" t="n">
         <v>0</v>
       </c>
+      <c r="D903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" s="2" t="n">
@@ -9995,6 +10902,7 @@
       <c r="C904" t="n">
         <v>1</v>
       </c>
+      <c r="D904" t="inlineStr"/>
     </row>
     <row r="905">
       <c r="A905" s="2" t="n">
@@ -10008,6 +10916,7 @@
       <c r="C905" t="n">
         <v>1</v>
       </c>
+      <c r="D905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" s="2" t="n">
@@ -10021,6 +10930,7 @@
       <c r="C906" t="n">
         <v>1</v>
       </c>
+      <c r="D906" t="inlineStr"/>
     </row>
     <row r="907">
       <c r="A907" s="2" t="n">
@@ -10034,6 +10944,7 @@
       <c r="C907" t="n">
         <v>1</v>
       </c>
+      <c r="D907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" s="2" t="n">
@@ -10047,6 +10958,7 @@
       <c r="C908" t="n">
         <v>1</v>
       </c>
+      <c r="D908" t="inlineStr"/>
     </row>
     <row r="909">
       <c r="A909" s="2" t="n">
@@ -10060,6 +10972,7 @@
       <c r="C909" t="n">
         <v>1</v>
       </c>
+      <c r="D909" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" s="2" t="n">
@@ -10073,6 +10986,7 @@
       <c r="C910" t="n">
         <v>1</v>
       </c>
+      <c r="D910" t="inlineStr"/>
     </row>
     <row r="911">
       <c r="A911" s="2" t="n">
@@ -10086,6 +11000,7 @@
       <c r="C911" t="n">
         <v>1</v>
       </c>
+      <c r="D911" t="inlineStr"/>
     </row>
     <row r="912">
       <c r="A912" s="2" t="n">
@@ -10099,6 +11014,7 @@
       <c r="C912" t="n">
         <v>1</v>
       </c>
+      <c r="D912" t="inlineStr"/>
     </row>
     <row r="913">
       <c r="A913" s="2" t="n">
@@ -10112,6 +11028,7 @@
       <c r="C913" t="n">
         <v>1</v>
       </c>
+      <c r="D913" t="inlineStr"/>
     </row>
     <row r="914">
       <c r="A914" s="2" t="n">
@@ -10121,6 +11038,7 @@
       <c r="C914" t="n">
         <v>0</v>
       </c>
+      <c r="D914" t="inlineStr"/>
     </row>
     <row r="915">
       <c r="A915" s="2" t="n">
@@ -10130,6 +11048,7 @@
       <c r="C915" t="n">
         <v>0</v>
       </c>
+      <c r="D915" t="inlineStr"/>
     </row>
     <row r="916">
       <c r="A916" s="2" t="n">
@@ -10139,6 +11058,7 @@
       <c r="C916" t="n">
         <v>0</v>
       </c>
+      <c r="D916" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="n">
@@ -10148,6 +11068,7 @@
       <c r="C917" t="n">
         <v>0</v>
       </c>
+      <c r="D917" t="inlineStr"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="n">
@@ -10157,6 +11078,7 @@
       <c r="C918" t="n">
         <v>0</v>
       </c>
+      <c r="D918" t="inlineStr"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="n">
@@ -10170,6 +11092,7 @@
       <c r="C919" t="n">
         <v>1</v>
       </c>
+      <c r="D919" t="inlineStr"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="n">
@@ -10183,6 +11106,7 @@
       <c r="C920" t="n">
         <v>1</v>
       </c>
+      <c r="D920" t="inlineStr"/>
     </row>
     <row r="921">
       <c r="A921" s="2" t="n">
@@ -10192,6 +11116,7 @@
       <c r="C921" t="n">
         <v>0</v>
       </c>
+      <c r="D921" t="inlineStr"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="n">
@@ -10201,6 +11126,7 @@
       <c r="C922" t="n">
         <v>0</v>
       </c>
+      <c r="D922" t="inlineStr"/>
     </row>
     <row r="923">
       <c r="A923" s="2" t="n">
@@ -10210,6 +11136,7 @@
       <c r="C923" t="n">
         <v>0</v>
       </c>
+      <c r="D923" t="inlineStr"/>
     </row>
     <row r="924">
       <c r="A924" s="2" t="n">
@@ -10219,6 +11146,7 @@
       <c r="C924" t="n">
         <v>0</v>
       </c>
+      <c r="D924" t="inlineStr"/>
     </row>
     <row r="925">
       <c r="A925" s="2" t="n">
@@ -10228,6 +11156,7 @@
       <c r="C925" t="n">
         <v>0</v>
       </c>
+      <c r="D925" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" s="2" t="n">
@@ -10241,6 +11170,7 @@
       <c r="C926" t="n">
         <v>1</v>
       </c>
+      <c r="D926" t="inlineStr"/>
     </row>
     <row r="927">
       <c r="A927" s="2" t="n">
@@ -10254,6 +11184,7 @@
       <c r="C927" t="n">
         <v>1</v>
       </c>
+      <c r="D927" t="inlineStr"/>
     </row>
     <row r="928">
       <c r="A928" s="2" t="n">
@@ -10263,6 +11194,7 @@
       <c r="C928" t="n">
         <v>0</v>
       </c>
+      <c r="D928" t="inlineStr"/>
     </row>
     <row r="929">
       <c r="A929" s="2" t="n">
@@ -10272,6 +11204,7 @@
       <c r="C929" t="n">
         <v>0</v>
       </c>
+      <c r="D929" t="inlineStr"/>
     </row>
     <row r="930">
       <c r="A930" s="2" t="n">
@@ -10281,6 +11214,7 @@
       <c r="C930" t="n">
         <v>0</v>
       </c>
+      <c r="D930" t="inlineStr"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="n">
@@ -10290,6 +11224,7 @@
       <c r="C931" t="n">
         <v>0</v>
       </c>
+      <c r="D931" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="n">
@@ -10299,6 +11234,7 @@
       <c r="C932" t="n">
         <v>0</v>
       </c>
+      <c r="D932" t="inlineStr"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="n">
@@ -10312,6 +11248,7 @@
       <c r="C933" t="n">
         <v>1</v>
       </c>
+      <c r="D933" t="inlineStr"/>
     </row>
     <row r="934">
       <c r="A934" s="2" t="n">
@@ -10325,6 +11262,7 @@
       <c r="C934" t="n">
         <v>1</v>
       </c>
+      <c r="D934" t="inlineStr"/>
     </row>
     <row r="935">
       <c r="A935" s="2" t="n">
@@ -10334,6 +11272,7 @@
       <c r="C935" t="n">
         <v>0</v>
       </c>
+      <c r="D935" t="inlineStr"/>
     </row>
     <row r="936">
       <c r="A936" s="2" t="n">
@@ -10343,6 +11282,7 @@
       <c r="C936" t="n">
         <v>0</v>
       </c>
+      <c r="D936" t="inlineStr"/>
     </row>
     <row r="937">
       <c r="A937" s="2" t="n">
@@ -10352,6 +11292,7 @@
       <c r="C937" t="n">
         <v>0</v>
       </c>
+      <c r="D937" t="inlineStr"/>
     </row>
     <row r="938">
       <c r="A938" s="2" t="n">
@@ -10361,6 +11302,7 @@
       <c r="C938" t="n">
         <v>0</v>
       </c>
+      <c r="D938" t="inlineStr"/>
     </row>
     <row r="939">
       <c r="A939" s="2" t="n">
@@ -10370,6 +11312,7 @@
       <c r="C939" t="n">
         <v>0</v>
       </c>
+      <c r="D939" t="inlineStr"/>
     </row>
     <row r="940">
       <c r="A940" s="2" t="n">
@@ -10383,6 +11326,7 @@
       <c r="C940" t="n">
         <v>1</v>
       </c>
+      <c r="D940" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" s="2" t="n">
@@ -10396,6 +11340,7 @@
       <c r="C941" t="n">
         <v>1</v>
       </c>
+      <c r="D941" t="inlineStr"/>
     </row>
     <row r="942">
       <c r="A942" s="2" t="n">
@@ -10405,6 +11350,7 @@
       <c r="C942" t="n">
         <v>0</v>
       </c>
+      <c r="D942" t="inlineStr"/>
     </row>
     <row r="943">
       <c r="A943" s="2" t="n">
@@ -10414,6 +11360,7 @@
       <c r="C943" t="n">
         <v>0</v>
       </c>
+      <c r="D943" t="inlineStr"/>
     </row>
     <row r="944">
       <c r="A944" s="2" t="n">
@@ -10423,6 +11370,7 @@
       <c r="C944" t="n">
         <v>0</v>
       </c>
+      <c r="D944" t="inlineStr"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="n">
@@ -10432,6 +11380,7 @@
       <c r="C945" t="n">
         <v>0</v>
       </c>
+      <c r="D945" t="inlineStr"/>
     </row>
     <row r="946">
       <c r="A946" s="2" t="n">
@@ -10441,6 +11390,7 @@
       <c r="C946" t="n">
         <v>0</v>
       </c>
+      <c r="D946" t="inlineStr"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="n">
@@ -10454,6 +11404,7 @@
       <c r="C947" t="n">
         <v>1</v>
       </c>
+      <c r="D947" t="inlineStr"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="n">
@@ -10467,6 +11418,7 @@
       <c r="C948" t="n">
         <v>1</v>
       </c>
+      <c r="D948" t="inlineStr"/>
     </row>
     <row r="949">
       <c r="A949" s="2" t="n">
@@ -10476,6 +11428,7 @@
       <c r="C949" t="n">
         <v>0</v>
       </c>
+      <c r="D949" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="n">
@@ -10485,6 +11438,7 @@
       <c r="C950" t="n">
         <v>0</v>
       </c>
+      <c r="D950" t="inlineStr"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="n">
@@ -10494,6 +11448,7 @@
       <c r="C951" t="n">
         <v>0</v>
       </c>
+      <c r="D951" t="inlineStr"/>
     </row>
     <row r="952">
       <c r="A952" s="2" t="n">
@@ -10503,6 +11458,7 @@
       <c r="C952" t="n">
         <v>0</v>
       </c>
+      <c r="D952" t="inlineStr"/>
     </row>
     <row r="953">
       <c r="A953" s="2" t="n">
@@ -10512,6 +11468,7 @@
       <c r="C953" t="n">
         <v>0</v>
       </c>
+      <c r="D953" t="inlineStr"/>
     </row>
     <row r="954">
       <c r="A954" s="2" t="n">
@@ -10525,6 +11482,7 @@
       <c r="C954" t="n">
         <v>1</v>
       </c>
+      <c r="D954" t="inlineStr"/>
     </row>
     <row r="955">
       <c r="A955" s="2" t="n">
@@ -10538,6 +11496,7 @@
       <c r="C955" t="n">
         <v>1</v>
       </c>
+      <c r="D955" t="inlineStr"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="n">
@@ -10547,6 +11506,7 @@
       <c r="C956" t="n">
         <v>0</v>
       </c>
+      <c r="D956" t="inlineStr"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="n">
@@ -10556,6 +11516,7 @@
       <c r="C957" t="n">
         <v>0</v>
       </c>
+      <c r="D957" t="inlineStr"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="n">
@@ -10565,6 +11526,7 @@
       <c r="C958" t="n">
         <v>0</v>
       </c>
+      <c r="D958" t="inlineStr"/>
     </row>
     <row r="959">
       <c r="A959" s="2" t="n">
@@ -10574,6 +11536,7 @@
       <c r="C959" t="n">
         <v>0</v>
       </c>
+      <c r="D959" t="inlineStr"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="n">
@@ -10583,6 +11546,7 @@
       <c r="C960" t="n">
         <v>0</v>
       </c>
+      <c r="D960" t="inlineStr"/>
     </row>
     <row r="961">
       <c r="A961" s="2" t="n">
@@ -10596,6 +11560,7 @@
       <c r="C961" t="n">
         <v>1</v>
       </c>
+      <c r="D961" t="inlineStr"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="n">
@@ -10609,6 +11574,7 @@
       <c r="C962" t="n">
         <v>1</v>
       </c>
+      <c r="D962" t="inlineStr"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="n">
@@ -10618,6 +11584,7 @@
       <c r="C963" t="n">
         <v>0</v>
       </c>
+      <c r="D963" t="inlineStr"/>
     </row>
     <row r="964">
       <c r="A964" s="2" t="n">
@@ -10627,6 +11594,7 @@
       <c r="C964" t="n">
         <v>0</v>
       </c>
+      <c r="D964" t="inlineStr"/>
     </row>
     <row r="965">
       <c r="A965" s="2" t="n">
@@ -10636,6 +11604,7 @@
       <c r="C965" t="n">
         <v>0</v>
       </c>
+      <c r="D965" t="inlineStr"/>
     </row>
     <row r="966">
       <c r="A966" s="2" t="n">
@@ -10645,6 +11614,7 @@
       <c r="C966" t="n">
         <v>0</v>
       </c>
+      <c r="D966" t="inlineStr"/>
     </row>
     <row r="967">
       <c r="A967" s="2" t="n">
@@ -10654,6 +11624,7 @@
       <c r="C967" t="n">
         <v>0</v>
       </c>
+      <c r="D967" t="inlineStr"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="n">
@@ -10667,6 +11638,7 @@
       <c r="C968" t="n">
         <v>1</v>
       </c>
+      <c r="D968" t="inlineStr"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="n">
@@ -10680,6 +11652,7 @@
       <c r="C969" t="n">
         <v>1</v>
       </c>
+      <c r="D969" t="inlineStr"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="n">
@@ -10689,6 +11662,7 @@
       <c r="C970" t="n">
         <v>0</v>
       </c>
+      <c r="D970" t="inlineStr"/>
     </row>
     <row r="971">
       <c r="A971" s="2" t="n">
@@ -10698,6 +11672,7 @@
       <c r="C971" t="n">
         <v>0</v>
       </c>
+      <c r="D971" t="inlineStr"/>
     </row>
     <row r="972">
       <c r="A972" s="2" t="n">
@@ -10707,6 +11682,7 @@
       <c r="C972" t="n">
         <v>0</v>
       </c>
+      <c r="D972" t="inlineStr"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="n">
@@ -10716,6 +11692,7 @@
       <c r="C973" t="n">
         <v>0</v>
       </c>
+      <c r="D973" t="inlineStr"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="n">
@@ -10725,6 +11702,7 @@
       <c r="C974" t="n">
         <v>0</v>
       </c>
+      <c r="D974" t="inlineStr"/>
     </row>
     <row r="975">
       <c r="A975" s="2" t="n">
@@ -10738,6 +11716,7 @@
       <c r="C975" t="n">
         <v>1</v>
       </c>
+      <c r="D975" t="inlineStr"/>
     </row>
     <row r="976">
       <c r="A976" s="2" t="n">
@@ -10751,6 +11730,7 @@
       <c r="C976" t="n">
         <v>1</v>
       </c>
+      <c r="D976" t="inlineStr"/>
     </row>
     <row r="977">
       <c r="A977" s="2" t="n">
@@ -10760,6 +11740,7 @@
       <c r="C977" t="n">
         <v>0</v>
       </c>
+      <c r="D977" t="inlineStr"/>
     </row>
     <row r="978">
       <c r="A978" s="2" t="n">
@@ -10769,6 +11750,7 @@
       <c r="C978" t="n">
         <v>0</v>
       </c>
+      <c r="D978" t="inlineStr"/>
     </row>
     <row r="979">
       <c r="A979" s="2" t="n">
@@ -10778,6 +11760,7 @@
       <c r="C979" t="n">
         <v>0</v>
       </c>
+      <c r="D979" t="inlineStr"/>
     </row>
     <row r="980">
       <c r="A980" s="2" t="n">
@@ -10787,6 +11770,7 @@
       <c r="C980" t="n">
         <v>0</v>
       </c>
+      <c r="D980" t="inlineStr"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="n">
@@ -10796,6 +11780,7 @@
       <c r="C981" t="n">
         <v>0</v>
       </c>
+      <c r="D981" t="inlineStr"/>
     </row>
     <row r="982">
       <c r="A982" s="2" t="n">
@@ -10809,6 +11794,7 @@
       <c r="C982" t="n">
         <v>1</v>
       </c>
+      <c r="D982" t="inlineStr"/>
     </row>
     <row r="983">
       <c r="A983" s="2" t="n">
@@ -10822,6 +11808,7 @@
       <c r="C983" t="n">
         <v>1</v>
       </c>
+      <c r="D983" t="inlineStr"/>
     </row>
     <row r="984">
       <c r="A984" s="2" t="n">
@@ -10831,6 +11818,7 @@
       <c r="C984" t="n">
         <v>0</v>
       </c>
+      <c r="D984" t="inlineStr"/>
     </row>
     <row r="985">
       <c r="A985" s="2" t="n">
@@ -10840,6 +11828,7 @@
       <c r="C985" t="n">
         <v>0</v>
       </c>
+      <c r="D985" t="inlineStr"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="n">
@@ -10849,6 +11838,7 @@
       <c r="C986" t="n">
         <v>0</v>
       </c>
+      <c r="D986" t="inlineStr"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="n">
@@ -10858,6 +11848,7 @@
       <c r="C987" t="n">
         <v>0</v>
       </c>
+      <c r="D987" t="inlineStr"/>
     </row>
     <row r="988">
       <c r="A988" s="2" t="n">
@@ -10867,6 +11858,7 @@
       <c r="C988" t="n">
         <v>0</v>
       </c>
+      <c r="D988" t="inlineStr"/>
     </row>
     <row r="989">
       <c r="A989" s="2" t="n">
@@ -10880,6 +11872,7 @@
       <c r="C989" t="n">
         <v>1</v>
       </c>
+      <c r="D989" t="inlineStr"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="n">
@@ -10893,6 +11886,7 @@
       <c r="C990" t="n">
         <v>1</v>
       </c>
+      <c r="D990" t="inlineStr"/>
     </row>
     <row r="991">
       <c r="A991" s="2" t="n">
@@ -10906,6 +11900,7 @@
       <c r="C991" t="n">
         <v>1</v>
       </c>
+      <c r="D991" t="inlineStr"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="n">
@@ -10915,6 +11910,7 @@
       <c r="C992" t="n">
         <v>0</v>
       </c>
+      <c r="D992" t="inlineStr"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="n">
@@ -10924,6 +11920,7 @@
       <c r="C993" t="n">
         <v>0</v>
       </c>
+      <c r="D993" t="inlineStr"/>
     </row>
     <row r="994">
       <c r="A994" s="2" t="n">
@@ -10933,6 +11930,7 @@
       <c r="C994" t="n">
         <v>0</v>
       </c>
+      <c r="D994" t="inlineStr"/>
     </row>
     <row r="995">
       <c r="A995" s="2" t="n">
@@ -10942,6 +11940,7 @@
       <c r="C995" t="n">
         <v>0</v>
       </c>
+      <c r="D995" t="inlineStr"/>
     </row>
     <row r="996">
       <c r="A996" s="2" t="n">
@@ -10955,6 +11954,7 @@
       <c r="C996" t="n">
         <v>1</v>
       </c>
+      <c r="D996" t="inlineStr"/>
     </row>
     <row r="997">
       <c r="A997" s="2" t="n">
@@ -10968,6 +11968,7 @@
       <c r="C997" t="n">
         <v>1</v>
       </c>
+      <c r="D997" t="inlineStr"/>
     </row>
     <row r="998">
       <c r="A998" s="2" t="n">
@@ -10977,6 +11978,7 @@
       <c r="C998" t="n">
         <v>0</v>
       </c>
+      <c r="D998" t="inlineStr"/>
     </row>
     <row r="999">
       <c r="A999" s="2" t="n">
@@ -10986,6 +11988,7 @@
       <c r="C999" t="n">
         <v>0</v>
       </c>
+      <c r="D999" t="inlineStr"/>
     </row>
     <row r="1000">
       <c r="A1000" s="2" t="n">
@@ -10995,6 +11998,7 @@
       <c r="C1000" t="n">
         <v>0</v>
       </c>
+      <c r="D1000" t="inlineStr"/>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="n">
@@ -11004,6 +12008,7 @@
       <c r="C1001" t="n">
         <v>0</v>
       </c>
+      <c r="D1001" t="inlineStr"/>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="n">
@@ -11013,6 +12018,7 @@
       <c r="C1002" t="n">
         <v>0</v>
       </c>
+      <c r="D1002" t="inlineStr"/>
     </row>
     <row r="1003">
       <c r="A1003" s="2" t="n">
@@ -11026,6 +12032,7 @@
       <c r="C1003" t="n">
         <v>1</v>
       </c>
+      <c r="D1003" t="inlineStr"/>
     </row>
     <row r="1004">
       <c r="A1004" s="2" t="n">
@@ -11039,6 +12046,7 @@
       <c r="C1004" t="n">
         <v>1</v>
       </c>
+      <c r="D1004" t="inlineStr"/>
     </row>
     <row r="1005">
       <c r="A1005" s="2" t="n">
@@ -11048,6 +12056,7 @@
       <c r="C1005" t="n">
         <v>0</v>
       </c>
+      <c r="D1005" t="inlineStr"/>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="n">
@@ -11057,6 +12066,7 @@
       <c r="C1006" t="n">
         <v>0</v>
       </c>
+      <c r="D1006" t="inlineStr"/>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="n">
@@ -11066,6 +12076,7 @@
       <c r="C1007" t="n">
         <v>0</v>
       </c>
+      <c r="D1007" t="inlineStr"/>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="n">
@@ -11075,6 +12086,7 @@
       <c r="C1008" t="n">
         <v>0</v>
       </c>
+      <c r="D1008" t="inlineStr"/>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="n">
@@ -11084,6 +12096,7 @@
       <c r="C1009" t="n">
         <v>0</v>
       </c>
+      <c r="D1009" t="inlineStr"/>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="n">
@@ -11097,6 +12110,7 @@
       <c r="C1010" t="n">
         <v>1</v>
       </c>
+      <c r="D1010" t="inlineStr"/>
     </row>
     <row r="1011">
       <c r="A1011" s="2" t="n">
@@ -11110,6 +12124,7 @@
       <c r="C1011" t="n">
         <v>1</v>
       </c>
+      <c r="D1011" t="inlineStr"/>
     </row>
     <row r="1012">
       <c r="A1012" s="2" t="n">
@@ -11119,6 +12134,7 @@
       <c r="C1012" t="n">
         <v>0</v>
       </c>
+      <c r="D1012" t="inlineStr"/>
     </row>
     <row r="1013">
       <c r="A1013" s="2" t="n">
@@ -11128,6 +12144,7 @@
       <c r="C1013" t="n">
         <v>0</v>
       </c>
+      <c r="D1013" t="inlineStr"/>
     </row>
     <row r="1014">
       <c r="A1014" s="2" t="n">
@@ -11137,6 +12154,7 @@
       <c r="C1014" t="n">
         <v>0</v>
       </c>
+      <c r="D1014" t="inlineStr"/>
     </row>
     <row r="1015">
       <c r="A1015" s="2" t="n">
@@ -11146,6 +12164,7 @@
       <c r="C1015" t="n">
         <v>0</v>
       </c>
+      <c r="D1015" t="inlineStr"/>
     </row>
     <row r="1016">
       <c r="A1016" s="2" t="n">
@@ -11155,6 +12174,7 @@
       <c r="C1016" t="n">
         <v>0</v>
       </c>
+      <c r="D1016" t="inlineStr"/>
     </row>
     <row r="1017">
       <c r="A1017" s="2" t="n">
@@ -11168,6 +12188,7 @@
       <c r="C1017" t="n">
         <v>1</v>
       </c>
+      <c r="D1017" t="inlineStr"/>
     </row>
     <row r="1018">
       <c r="A1018" s="2" t="n">
@@ -11181,6 +12202,7 @@
       <c r="C1018" t="n">
         <v>1</v>
       </c>
+      <c r="D1018" t="inlineStr"/>
     </row>
     <row r="1019">
       <c r="A1019" s="2" t="n">
@@ -11190,6 +12212,7 @@
       <c r="C1019" t="n">
         <v>0</v>
       </c>
+      <c r="D1019" t="inlineStr"/>
     </row>
     <row r="1020">
       <c r="A1020" s="2" t="n">
@@ -11199,6 +12222,7 @@
       <c r="C1020" t="n">
         <v>0</v>
       </c>
+      <c r="D1020" t="inlineStr"/>
     </row>
     <row r="1021">
       <c r="A1021" s="2" t="n">
@@ -11208,6 +12232,7 @@
       <c r="C1021" t="n">
         <v>0</v>
       </c>
+      <c r="D1021" t="inlineStr"/>
     </row>
     <row r="1022">
       <c r="A1022" s="2" t="n">
@@ -11217,6 +12242,7 @@
       <c r="C1022" t="n">
         <v>0</v>
       </c>
+      <c r="D1022" t="inlineStr"/>
     </row>
     <row r="1023">
       <c r="A1023" s="2" t="n">
@@ -11226,6 +12252,7 @@
       <c r="C1023" t="n">
         <v>0</v>
       </c>
+      <c r="D1023" t="inlineStr"/>
     </row>
     <row r="1024">
       <c r="A1024" s="2" t="n">
@@ -11239,6 +12266,7 @@
       <c r="C1024" t="n">
         <v>1</v>
       </c>
+      <c r="D1024" t="inlineStr"/>
     </row>
     <row r="1025">
       <c r="A1025" s="2" t="n">
@@ -11252,6 +12280,7 @@
       <c r="C1025" t="n">
         <v>1</v>
       </c>
+      <c r="D1025" t="inlineStr"/>
     </row>
     <row r="1026">
       <c r="A1026" s="2" t="n">
@@ -11261,6 +12290,7 @@
       <c r="C1026" t="n">
         <v>0</v>
       </c>
+      <c r="D1026" t="inlineStr"/>
     </row>
     <row r="1027">
       <c r="A1027" s="2" t="n">
@@ -11270,6 +12300,7 @@
       <c r="C1027" t="n">
         <v>0</v>
       </c>
+      <c r="D1027" t="inlineStr"/>
     </row>
     <row r="1028">
       <c r="A1028" s="2" t="n">
@@ -11279,6 +12310,7 @@
       <c r="C1028" t="n">
         <v>0</v>
       </c>
+      <c r="D1028" t="inlineStr"/>
     </row>
     <row r="1029">
       <c r="A1029" s="2" t="n">
@@ -11288,6 +12320,7 @@
       <c r="C1029" t="n">
         <v>0</v>
       </c>
+      <c r="D1029" t="inlineStr"/>
     </row>
     <row r="1030">
       <c r="A1030" s="2" t="n">
@@ -11297,6 +12330,7 @@
       <c r="C1030" t="n">
         <v>0</v>
       </c>
+      <c r="D1030" t="inlineStr"/>
     </row>
     <row r="1031">
       <c r="A1031" s="2" t="n">
@@ -11310,6 +12344,7 @@
       <c r="C1031" t="n">
         <v>1</v>
       </c>
+      <c r="D1031" t="inlineStr"/>
     </row>
     <row r="1032">
       <c r="A1032" s="2" t="n">
@@ -11323,6 +12358,7 @@
       <c r="C1032" t="n">
         <v>1</v>
       </c>
+      <c r="D1032" t="inlineStr"/>
     </row>
     <row r="1033">
       <c r="A1033" s="2" t="n">
@@ -11332,6 +12368,7 @@
       <c r="C1033" t="n">
         <v>0</v>
       </c>
+      <c r="D1033" t="inlineStr"/>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="n">
@@ -11341,6 +12378,7 @@
       <c r="C1034" t="n">
         <v>0</v>
       </c>
+      <c r="D1034" t="inlineStr"/>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="n">
@@ -11350,6 +12388,7 @@
       <c r="C1035" t="n">
         <v>0</v>
       </c>
+      <c r="D1035" t="inlineStr"/>
     </row>
     <row r="1036">
       <c r="A1036" s="2" t="n">
@@ -11359,6 +12398,7 @@
       <c r="C1036" t="n">
         <v>0</v>
       </c>
+      <c r="D1036" t="inlineStr"/>
     </row>
     <row r="1037">
       <c r="A1037" s="2" t="n">
@@ -11368,6 +12408,7 @@
       <c r="C1037" t="n">
         <v>0</v>
       </c>
+      <c r="D1037" t="inlineStr"/>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="n">
@@ -11381,6 +12422,7 @@
       <c r="C1038" t="n">
         <v>1</v>
       </c>
+      <c r="D1038" t="inlineStr"/>
     </row>
     <row r="1039">
       <c r="A1039" s="2" t="n">
@@ -11394,6 +12436,7 @@
       <c r="C1039" t="n">
         <v>1</v>
       </c>
+      <c r="D1039" t="inlineStr"/>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="n">
@@ -11403,6 +12446,7 @@
       <c r="C1040" t="n">
         <v>0</v>
       </c>
+      <c r="D1040" t="inlineStr"/>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="n">
@@ -11412,6 +12456,7 @@
       <c r="C1041" t="n">
         <v>0</v>
       </c>
+      <c r="D1041" t="inlineStr"/>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="n">
@@ -11421,6 +12466,7 @@
       <c r="C1042" t="n">
         <v>0</v>
       </c>
+      <c r="D1042" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="n">
@@ -11430,6 +12476,7 @@
       <c r="C1043" t="n">
         <v>0</v>
       </c>
+      <c r="D1043" t="inlineStr"/>
     </row>
     <row r="1044">
       <c r="A1044" s="2" t="n">
@@ -11439,6 +12486,7 @@
       <c r="C1044" t="n">
         <v>0</v>
       </c>
+      <c r="D1044" t="inlineStr"/>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="n">
@@ -11452,6 +12500,7 @@
       <c r="C1045" t="n">
         <v>1</v>
       </c>
+      <c r="D1045" t="inlineStr"/>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="n">
@@ -11465,6 +12514,7 @@
       <c r="C1046" t="n">
         <v>1</v>
       </c>
+      <c r="D1046" t="inlineStr"/>
     </row>
     <row r="1047">
       <c r="A1047" s="2" t="n">
@@ -11474,6 +12524,7 @@
       <c r="C1047" t="n">
         <v>0</v>
       </c>
+      <c r="D1047" t="inlineStr"/>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="n">
@@ -11483,6 +12534,7 @@
       <c r="C1048" t="n">
         <v>0</v>
       </c>
+      <c r="D1048" t="inlineStr"/>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="n">
@@ -11492,6 +12544,7 @@
       <c r="C1049" t="n">
         <v>0</v>
       </c>
+      <c r="D1049" t="inlineStr"/>
     </row>
     <row r="1050">
       <c r="A1050" s="2" t="n">
@@ -11501,6 +12554,7 @@
       <c r="C1050" t="n">
         <v>0</v>
       </c>
+      <c r="D1050" t="inlineStr"/>
     </row>
     <row r="1051">
       <c r="A1051" s="2" t="n">
@@ -11510,6 +12564,7 @@
       <c r="C1051" t="n">
         <v>0</v>
       </c>
+      <c r="D1051" t="inlineStr"/>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="n">
@@ -11523,6 +12578,7 @@
       <c r="C1052" t="n">
         <v>1</v>
       </c>
+      <c r="D1052" t="inlineStr"/>
     </row>
     <row r="1053">
       <c r="A1053" s="2" t="n">
@@ -11536,6 +12592,7 @@
       <c r="C1053" t="n">
         <v>1</v>
       </c>
+      <c r="D1053" t="inlineStr"/>
     </row>
     <row r="1054">
       <c r="A1054" s="2" t="n">
@@ -11545,6 +12602,7 @@
       <c r="C1054" t="n">
         <v>0</v>
       </c>
+      <c r="D1054" t="inlineStr"/>
     </row>
     <row r="1055">
       <c r="A1055" s="2" t="n">
@@ -11554,6 +12612,7 @@
       <c r="C1055" t="n">
         <v>0</v>
       </c>
+      <c r="D1055" t="inlineStr"/>
     </row>
     <row r="1056">
       <c r="A1056" s="2" t="n">
@@ -11563,6 +12622,7 @@
       <c r="C1056" t="n">
         <v>0</v>
       </c>
+      <c r="D1056" t="inlineStr"/>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="n">
@@ -11572,6 +12632,7 @@
       <c r="C1057" t="n">
         <v>0</v>
       </c>
+      <c r="D1057" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="n">
@@ -11581,6 +12642,7 @@
       <c r="C1058" t="n">
         <v>0</v>
       </c>
+      <c r="D1058" t="inlineStr"/>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="n">
@@ -11594,6 +12656,7 @@
       <c r="C1059" t="n">
         <v>1</v>
       </c>
+      <c r="D1059" t="inlineStr"/>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="n">
@@ -11607,6 +12670,7 @@
       <c r="C1060" t="n">
         <v>1</v>
       </c>
+      <c r="D1060" t="inlineStr"/>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="n">
@@ -11616,6 +12680,7 @@
       <c r="C1061" t="n">
         <v>0</v>
       </c>
+      <c r="D1061" t="inlineStr"/>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="n">
@@ -11625,6 +12690,7 @@
       <c r="C1062" t="n">
         <v>0</v>
       </c>
+      <c r="D1062" t="inlineStr"/>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="n">
@@ -11638,6 +12704,7 @@
       <c r="C1063" t="n">
         <v>1</v>
       </c>
+      <c r="D1063" t="inlineStr"/>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="n">
@@ -11647,6 +12714,7 @@
       <c r="C1064" t="n">
         <v>0</v>
       </c>
+      <c r="D1064" t="inlineStr"/>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="n">
@@ -11656,6 +12724,7 @@
       <c r="C1065" t="n">
         <v>0</v>
       </c>
+      <c r="D1065" t="inlineStr"/>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="n">
@@ -11669,6 +12738,7 @@
       <c r="C1066" t="n">
         <v>1</v>
       </c>
+      <c r="D1066" t="inlineStr"/>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="n">
@@ -11682,6 +12752,7 @@
       <c r="C1067" t="n">
         <v>1</v>
       </c>
+      <c r="D1067" t="inlineStr"/>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="n">
@@ -11691,6 +12762,7 @@
       <c r="C1068" t="n">
         <v>0</v>
       </c>
+      <c r="D1068" t="inlineStr"/>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="n">
@@ -11700,6 +12772,7 @@
       <c r="C1069" t="n">
         <v>0</v>
       </c>
+      <c r="D1069" t="inlineStr"/>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="n">
@@ -11709,6 +12782,7 @@
       <c r="C1070" t="n">
         <v>0</v>
       </c>
+      <c r="D1070" t="inlineStr"/>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="n">
@@ -11718,6 +12792,7 @@
       <c r="C1071" t="n">
         <v>0</v>
       </c>
+      <c r="D1071" t="inlineStr"/>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="n">
@@ -11727,6 +12802,7 @@
       <c r="C1072" t="n">
         <v>0</v>
       </c>
+      <c r="D1072" t="inlineStr"/>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="n">
@@ -11740,6 +12816,7 @@
       <c r="C1073" t="n">
         <v>1</v>
       </c>
+      <c r="D1073" t="inlineStr"/>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="n">
@@ -11753,6 +12830,7 @@
       <c r="C1074" t="n">
         <v>1</v>
       </c>
+      <c r="D1074" t="inlineStr"/>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="n">
@@ -11762,6 +12840,7 @@
       <c r="C1075" t="n">
         <v>0</v>
       </c>
+      <c r="D1075" t="inlineStr"/>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="n">
@@ -11771,6 +12850,7 @@
       <c r="C1076" t="n">
         <v>0</v>
       </c>
+      <c r="D1076" t="inlineStr"/>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="n">
@@ -11780,6 +12860,7 @@
       <c r="C1077" t="n">
         <v>0</v>
       </c>
+      <c r="D1077" t="inlineStr"/>
     </row>
     <row r="1078">
       <c r="A1078" s="2" t="n">
@@ -11789,6 +12870,7 @@
       <c r="C1078" t="n">
         <v>0</v>
       </c>
+      <c r="D1078" t="inlineStr"/>
     </row>
     <row r="1079">
       <c r="A1079" s="2" t="n">
@@ -11798,6 +12880,7 @@
       <c r="C1079" t="n">
         <v>0</v>
       </c>
+      <c r="D1079" t="inlineStr"/>
     </row>
     <row r="1080">
       <c r="A1080" s="2" t="n">
@@ -11811,6 +12894,7 @@
       <c r="C1080" t="n">
         <v>1</v>
       </c>
+      <c r="D1080" t="inlineStr"/>
     </row>
     <row r="1081">
       <c r="A1081" s="2" t="n">
@@ -11824,6 +12908,7 @@
       <c r="C1081" t="n">
         <v>1</v>
       </c>
+      <c r="D1081" t="inlineStr"/>
     </row>
     <row r="1082">
       <c r="A1082" s="2" t="n">
@@ -11833,6 +12918,7 @@
       <c r="C1082" t="n">
         <v>0</v>
       </c>
+      <c r="D1082" t="inlineStr"/>
     </row>
     <row r="1083">
       <c r="A1083" s="2" t="n">
@@ -11842,6 +12928,7 @@
       <c r="C1083" t="n">
         <v>0</v>
       </c>
+      <c r="D1083" t="inlineStr"/>
     </row>
     <row r="1084">
       <c r="A1084" s="2" t="n">
@@ -11851,6 +12938,7 @@
       <c r="C1084" t="n">
         <v>0</v>
       </c>
+      <c r="D1084" t="inlineStr"/>
     </row>
     <row r="1085">
       <c r="A1085" s="2" t="n">
@@ -11860,6 +12948,7 @@
       <c r="C1085" t="n">
         <v>0</v>
       </c>
+      <c r="D1085" t="inlineStr"/>
     </row>
     <row r="1086">
       <c r="A1086" s="2" t="n">
@@ -11869,6 +12958,7 @@
       <c r="C1086" t="n">
         <v>0</v>
       </c>
+      <c r="D1086" t="inlineStr"/>
     </row>
     <row r="1087">
       <c r="A1087" s="2" t="n">
@@ -11882,6 +12972,7 @@
       <c r="C1087" t="n">
         <v>1</v>
       </c>
+      <c r="D1087" t="inlineStr"/>
     </row>
     <row r="1088">
       <c r="A1088" s="2" t="n">
@@ -11895,6 +12986,7 @@
       <c r="C1088" t="n">
         <v>1</v>
       </c>
+      <c r="D1088" t="inlineStr"/>
     </row>
     <row r="1089">
       <c r="A1089" s="2" t="n">
@@ -11908,6 +13000,7 @@
       <c r="C1089" t="n">
         <v>1</v>
       </c>
+      <c r="D1089" t="inlineStr"/>
     </row>
     <row r="1090">
       <c r="A1090" s="2" t="n">
@@ -11921,6 +13014,7 @@
       <c r="C1090" t="n">
         <v>1</v>
       </c>
+      <c r="D1090" t="inlineStr"/>
     </row>
     <row r="1091">
       <c r="A1091" s="2" t="n">
@@ -11934,6 +13028,7 @@
       <c r="C1091" t="n">
         <v>1</v>
       </c>
+      <c r="D1091" t="inlineStr"/>
     </row>
     <row r="1092">
       <c r="A1092" s="2" t="n">
@@ -11947,6 +13042,7 @@
       <c r="C1092" t="n">
         <v>1</v>
       </c>
+      <c r="D1092" t="inlineStr"/>
     </row>
     <row r="1093">
       <c r="A1093" s="2" t="n">
@@ -11960,6 +13056,7 @@
       <c r="C1093" t="n">
         <v>1</v>
       </c>
+      <c r="D1093" t="inlineStr"/>
     </row>
     <row r="1094">
       <c r="A1094" s="2" t="n">
@@ -11973,6 +13070,7 @@
       <c r="C1094" t="n">
         <v>1</v>
       </c>
+      <c r="D1094" t="inlineStr"/>
     </row>
     <row r="1095">
       <c r="A1095" s="2" t="n">
@@ -11986,6 +13084,7 @@
       <c r="C1095" t="n">
         <v>1</v>
       </c>
+      <c r="D1095" t="inlineStr"/>
     </row>
     <row r="1096">
       <c r="A1096" s="2" t="n">
@@ -11999,6 +13098,7 @@
       <c r="C1096" t="n">
         <v>1</v>
       </c>
+      <c r="D1096" t="inlineStr"/>
     </row>
     <row r="1097">
       <c r="A1097" s="2" t="n">
@@ -12012,6 +13112,7 @@
       <c r="C1097" t="n">
         <v>1</v>
       </c>
+      <c r="D1097" t="inlineStr"/>
     </row>
     <row r="1098">
       <c r="A1098" s="2" t="n">
@@ -12025,6 +13126,7 @@
       <c r="C1098" t="n">
         <v>1</v>
       </c>
+      <c r="D1098" t="inlineStr"/>
     </row>
     <row r="1099">
       <c r="A1099" s="2" t="n">
@@ -12038,6 +13140,7 @@
       <c r="C1099" t="n">
         <v>1</v>
       </c>
+      <c r="D1099" t="inlineStr"/>
     </row>
     <row r="1100">
       <c r="A1100" s="2" t="n">
@@ -12051,6 +13154,7 @@
       <c r="C1100" t="n">
         <v>1</v>
       </c>
+      <c r="D1100" t="inlineStr"/>
     </row>
     <row r="1101">
       <c r="A1101" s="2" t="n">
@@ -12064,6 +13168,7 @@
       <c r="C1101" t="n">
         <v>1</v>
       </c>
+      <c r="D1101" t="inlineStr"/>
     </row>
     <row r="1102">
       <c r="A1102" s="2" t="n">
@@ -12077,6 +13182,7 @@
       <c r="C1102" t="n">
         <v>1</v>
       </c>
+      <c r="D1102" t="inlineStr"/>
     </row>
     <row r="1103">
       <c r="A1103" s="2" t="n">
@@ -12086,6 +13192,7 @@
       <c r="C1103" t="n">
         <v>0</v>
       </c>
+      <c r="D1103" t="inlineStr"/>
     </row>
     <row r="1104">
       <c r="A1104" s="2" t="n">
@@ -12095,6 +13202,7 @@
       <c r="C1104" t="n">
         <v>0</v>
       </c>
+      <c r="D1104" t="inlineStr"/>
     </row>
     <row r="1105">
       <c r="A1105" s="2" t="n">
@@ -12104,6 +13212,7 @@
       <c r="C1105" t="n">
         <v>0</v>
       </c>
+      <c r="D1105" t="inlineStr"/>
     </row>
     <row r="1106">
       <c r="A1106" s="2" t="n">
@@ -12113,6 +13222,7 @@
       <c r="C1106" t="n">
         <v>0</v>
       </c>
+      <c r="D1106" t="inlineStr"/>
     </row>
     <row r="1107">
       <c r="A1107" s="2" t="n">
@@ -12122,6 +13232,7 @@
       <c r="C1107" t="n">
         <v>0</v>
       </c>
+      <c r="D1107" t="inlineStr"/>
     </row>
     <row r="1108">
       <c r="A1108" s="2" t="n">
@@ -12135,6 +13246,7 @@
       <c r="C1108" t="n">
         <v>1</v>
       </c>
+      <c r="D1108" t="inlineStr"/>
     </row>
     <row r="1109">
       <c r="A1109" s="2" t="n">
@@ -12148,6 +13260,7 @@
       <c r="C1109" t="n">
         <v>1</v>
       </c>
+      <c r="D1109" t="inlineStr"/>
     </row>
     <row r="1110">
       <c r="A1110" s="2" t="n">
@@ -12157,6 +13270,7 @@
       <c r="C1110" t="n">
         <v>0</v>
       </c>
+      <c r="D1110" t="inlineStr"/>
     </row>
     <row r="1111">
       <c r="A1111" s="2" t="n">
@@ -12166,6 +13280,7 @@
       <c r="C1111" t="n">
         <v>0</v>
       </c>
+      <c r="D1111" t="inlineStr"/>
     </row>
     <row r="1112">
       <c r="A1112" s="2" t="n">
@@ -12175,6 +13290,7 @@
       <c r="C1112" t="n">
         <v>0</v>
       </c>
+      <c r="D1112" t="inlineStr"/>
     </row>
     <row r="1113">
       <c r="A1113" s="2" t="n">
@@ -12184,6 +13300,7 @@
       <c r="C1113" t="n">
         <v>0</v>
       </c>
+      <c r="D1113" t="inlineStr"/>
     </row>
     <row r="1114">
       <c r="A1114" s="2" t="n">
@@ -12193,6 +13310,7 @@
       <c r="C1114" t="n">
         <v>0</v>
       </c>
+      <c r="D1114" t="inlineStr"/>
     </row>
     <row r="1115">
       <c r="A1115" s="2" t="n">
@@ -12206,6 +13324,7 @@
       <c r="C1115" t="n">
         <v>1</v>
       </c>
+      <c r="D1115" t="inlineStr"/>
     </row>
     <row r="1116">
       <c r="A1116" s="2" t="n">
@@ -12219,6 +13338,7 @@
       <c r="C1116" t="n">
         <v>1</v>
       </c>
+      <c r="D1116" t="inlineStr"/>
     </row>
     <row r="1117">
       <c r="A1117" s="2" t="n">
@@ -12228,6 +13348,7 @@
       <c r="C1117" t="n">
         <v>0</v>
       </c>
+      <c r="D1117" t="inlineStr"/>
     </row>
     <row r="1118">
       <c r="A1118" s="2" t="n">
@@ -12237,6 +13358,7 @@
       <c r="C1118" t="n">
         <v>0</v>
       </c>
+      <c r="D1118" t="inlineStr"/>
     </row>
     <row r="1119">
       <c r="A1119" s="2" t="n">
@@ -12246,6 +13368,7 @@
       <c r="C1119" t="n">
         <v>0</v>
       </c>
+      <c r="D1119" t="inlineStr"/>
     </row>
     <row r="1120">
       <c r="A1120" s="2" t="n">
@@ -12255,6 +13378,7 @@
       <c r="C1120" t="n">
         <v>0</v>
       </c>
+      <c r="D1120" t="inlineStr"/>
     </row>
     <row r="1121">
       <c r="A1121" s="2" t="n">
@@ -12264,6 +13388,7 @@
       <c r="C1121" t="n">
         <v>0</v>
       </c>
+      <c r="D1121" t="inlineStr"/>
     </row>
     <row r="1122">
       <c r="A1122" s="2" t="n">
@@ -12277,6 +13402,7 @@
       <c r="C1122" t="n">
         <v>1</v>
       </c>
+      <c r="D1122" t="inlineStr"/>
     </row>
     <row r="1123">
       <c r="A1123" s="2" t="n">
@@ -12290,6 +13416,7 @@
       <c r="C1123" t="n">
         <v>1</v>
       </c>
+      <c r="D1123" t="inlineStr"/>
     </row>
     <row r="1124">
       <c r="A1124" s="2" t="n">
@@ -12303,6 +13430,7 @@
       <c r="C1124" t="n">
         <v>1</v>
       </c>
+      <c r="D1124" t="inlineStr"/>
     </row>
     <row r="1125">
       <c r="A1125" s="2" t="n">
@@ -12312,6 +13440,7 @@
       <c r="C1125" t="n">
         <v>0</v>
       </c>
+      <c r="D1125" t="inlineStr"/>
     </row>
     <row r="1126">
       <c r="A1126" s="2" t="n">
@@ -12325,6 +13454,7 @@
       <c r="C1126" t="n">
         <v>1</v>
       </c>
+      <c r="D1126" t="inlineStr"/>
     </row>
     <row r="1127">
       <c r="A1127" s="2" t="n">
@@ -12334,6 +13464,7 @@
       <c r="C1127" t="n">
         <v>0</v>
       </c>
+      <c r="D1127" t="inlineStr"/>
     </row>
     <row r="1128">
       <c r="A1128" s="2" t="n">
@@ -12343,6 +13474,7 @@
       <c r="C1128" t="n">
         <v>0</v>
       </c>
+      <c r="D1128" t="inlineStr"/>
     </row>
     <row r="1129">
       <c r="A1129" s="2" t="n">
@@ -12356,6 +13488,7 @@
       <c r="C1129" t="n">
         <v>1</v>
       </c>
+      <c r="D1129" t="inlineStr"/>
     </row>
     <row r="1130">
       <c r="A1130" s="2" t="n">
@@ -12369,6 +13502,7 @@
       <c r="C1130" t="n">
         <v>1</v>
       </c>
+      <c r="D1130" t="inlineStr"/>
     </row>
     <row r="1131">
       <c r="A1131" s="2" t="n">
@@ -12378,6 +13512,7 @@
       <c r="C1131" t="n">
         <v>0</v>
       </c>
+      <c r="D1131" t="inlineStr"/>
     </row>
     <row r="1132">
       <c r="A1132" s="2" t="n">
@@ -12387,6 +13522,7 @@
       <c r="C1132" t="n">
         <v>0</v>
       </c>
+      <c r="D1132" t="inlineStr"/>
     </row>
     <row r="1133">
       <c r="A1133" s="2" t="n">
@@ -12396,6 +13532,7 @@
       <c r="C1133" t="n">
         <v>0</v>
       </c>
+      <c r="D1133" t="inlineStr"/>
     </row>
     <row r="1134">
       <c r="A1134" s="2" t="n">
@@ -12405,6 +13542,7 @@
       <c r="C1134" t="n">
         <v>0</v>
       </c>
+      <c r="D1134" t="inlineStr"/>
     </row>
     <row r="1135">
       <c r="A1135" s="2" t="n">
@@ -12414,6 +13552,7 @@
       <c r="C1135" t="n">
         <v>0</v>
       </c>
+      <c r="D1135" t="inlineStr"/>
     </row>
     <row r="1136">
       <c r="A1136" s="2" t="n">
@@ -12427,6 +13566,7 @@
       <c r="C1136" t="n">
         <v>1</v>
       </c>
+      <c r="D1136" t="inlineStr"/>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="n">
@@ -12440,6 +13580,7 @@
       <c r="C1137" t="n">
         <v>1</v>
       </c>
+      <c r="D1137" t="inlineStr"/>
     </row>
     <row r="1138">
       <c r="A1138" s="2" t="n">
@@ -12449,6 +13590,7 @@
       <c r="C1138" t="n">
         <v>0</v>
       </c>
+      <c r="D1138" t="inlineStr"/>
     </row>
     <row r="1139">
       <c r="A1139" s="2" t="n">
@@ -12458,6 +13600,7 @@
       <c r="C1139" t="n">
         <v>0</v>
       </c>
+      <c r="D1139" t="inlineStr"/>
     </row>
     <row r="1140">
       <c r="A1140" s="2" t="n">
@@ -12467,6 +13610,7 @@
       <c r="C1140" t="n">
         <v>0</v>
       </c>
+      <c r="D1140" t="inlineStr"/>
     </row>
     <row r="1141">
       <c r="A1141" s="2" t="n">
@@ -12476,6 +13620,7 @@
       <c r="C1141" t="n">
         <v>0</v>
       </c>
+      <c r="D1141" t="inlineStr"/>
     </row>
     <row r="1142">
       <c r="A1142" s="2" t="n">
@@ -12485,6 +13630,7 @@
       <c r="C1142" t="n">
         <v>0</v>
       </c>
+      <c r="D1142" t="inlineStr"/>
     </row>
     <row r="1143">
       <c r="A1143" s="2" t="n">
@@ -12498,6 +13644,7 @@
       <c r="C1143" t="n">
         <v>1</v>
       </c>
+      <c r="D1143" t="inlineStr"/>
     </row>
     <row r="1144">
       <c r="A1144" s="2" t="n">
@@ -12511,6 +13658,7 @@
       <c r="C1144" t="n">
         <v>1</v>
       </c>
+      <c r="D1144" t="inlineStr"/>
     </row>
     <row r="1145">
       <c r="A1145" s="2" t="n">
@@ -12520,6 +13668,7 @@
       <c r="C1145" t="n">
         <v>0</v>
       </c>
+      <c r="D1145" t="inlineStr"/>
     </row>
     <row r="1146">
       <c r="A1146" s="2" t="n">
@@ -12529,6 +13678,7 @@
       <c r="C1146" t="n">
         <v>0</v>
       </c>
+      <c r="D1146" t="inlineStr"/>
     </row>
     <row r="1147">
       <c r="A1147" s="2" t="n">
@@ -12538,6 +13688,7 @@
       <c r="C1147" t="n">
         <v>0</v>
       </c>
+      <c r="D1147" t="inlineStr"/>
     </row>
     <row r="1148">
       <c r="A1148" s="2" t="n">
@@ -12547,6 +13698,7 @@
       <c r="C1148" t="n">
         <v>0</v>
       </c>
+      <c r="D1148" t="inlineStr"/>
     </row>
     <row r="1149">
       <c r="A1149" s="2" t="n">
@@ -12556,6 +13708,7 @@
       <c r="C1149" t="n">
         <v>0</v>
       </c>
+      <c r="D1149" t="inlineStr"/>
     </row>
     <row r="1150">
       <c r="A1150" s="2" t="n">
@@ -12569,6 +13722,7 @@
       <c r="C1150" t="n">
         <v>1</v>
       </c>
+      <c r="D1150" t="inlineStr"/>
     </row>
     <row r="1151">
       <c r="A1151" s="2" t="n">
@@ -12582,6 +13736,7 @@
       <c r="C1151" t="n">
         <v>1</v>
       </c>
+      <c r="D1151" t="inlineStr"/>
     </row>
     <row r="1152">
       <c r="A1152" s="2" t="n">
@@ -12591,6 +13746,7 @@
       <c r="C1152" t="n">
         <v>0</v>
       </c>
+      <c r="D1152" t="inlineStr"/>
     </row>
     <row r="1153">
       <c r="A1153" s="2" t="n">
@@ -12600,6 +13756,7 @@
       <c r="C1153" t="n">
         <v>0</v>
       </c>
+      <c r="D1153" t="inlineStr"/>
     </row>
     <row r="1154">
       <c r="A1154" s="2" t="n">
@@ -12609,6 +13766,7 @@
       <c r="C1154" t="n">
         <v>0</v>
       </c>
+      <c r="D1154" t="inlineStr"/>
     </row>
     <row r="1155">
       <c r="A1155" s="2" t="n">
@@ -12618,6 +13776,7 @@
       <c r="C1155" t="n">
         <v>0</v>
       </c>
+      <c r="D1155" t="inlineStr"/>
     </row>
     <row r="1156">
       <c r="A1156" s="2" t="n">
@@ -12627,6 +13786,7 @@
       <c r="C1156" t="n">
         <v>0</v>
       </c>
+      <c r="D1156" t="inlineStr"/>
     </row>
     <row r="1157">
       <c r="A1157" s="2" t="n">
@@ -12640,6 +13800,7 @@
       <c r="C1157" t="n">
         <v>1</v>
       </c>
+      <c r="D1157" t="inlineStr"/>
     </row>
     <row r="1158">
       <c r="A1158" s="2" t="n">
@@ -12653,6 +13814,7 @@
       <c r="C1158" t="n">
         <v>1</v>
       </c>
+      <c r="D1158" t="inlineStr"/>
     </row>
     <row r="1159">
       <c r="A1159" s="2" t="n">
@@ -12662,6 +13824,7 @@
       <c r="C1159" t="n">
         <v>0</v>
       </c>
+      <c r="D1159" t="inlineStr"/>
     </row>
     <row r="1160">
       <c r="A1160" s="2" t="n">
@@ -12671,6 +13834,7 @@
       <c r="C1160" t="n">
         <v>0</v>
       </c>
+      <c r="D1160" t="inlineStr"/>
     </row>
     <row r="1161">
       <c r="A1161" s="2" t="n">
@@ -12680,6 +13844,7 @@
       <c r="C1161" t="n">
         <v>0</v>
       </c>
+      <c r="D1161" t="inlineStr"/>
     </row>
     <row r="1162">
       <c r="A1162" s="2" t="n">
@@ -12689,6 +13854,7 @@
       <c r="C1162" t="n">
         <v>0</v>
       </c>
+      <c r="D1162" t="inlineStr"/>
     </row>
     <row r="1163">
       <c r="A1163" s="2" t="n">
@@ -12698,6 +13864,7 @@
       <c r="C1163" t="n">
         <v>0</v>
       </c>
+      <c r="D1163" t="inlineStr"/>
     </row>
     <row r="1164">
       <c r="A1164" s="2" t="n">
@@ -12711,6 +13878,7 @@
       <c r="C1164" t="n">
         <v>1</v>
       </c>
+      <c r="D1164" t="inlineStr"/>
     </row>
     <row r="1165">
       <c r="A1165" s="2" t="n">
@@ -12724,6 +13892,7 @@
       <c r="C1165" t="n">
         <v>1</v>
       </c>
+      <c r="D1165" t="inlineStr"/>
     </row>
     <row r="1166">
       <c r="A1166" s="2" t="n">
@@ -12733,6 +13902,7 @@
       <c r="C1166" t="n">
         <v>0</v>
       </c>
+      <c r="D1166" t="inlineStr"/>
     </row>
     <row r="1167">
       <c r="A1167" s="2" t="n">
@@ -12742,6 +13912,7 @@
       <c r="C1167" t="n">
         <v>0</v>
       </c>
+      <c r="D1167" t="inlineStr"/>
     </row>
     <row r="1168">
       <c r="A1168" s="2" t="n">
@@ -12751,6 +13922,7 @@
       <c r="C1168" t="n">
         <v>0</v>
       </c>
+      <c r="D1168" t="inlineStr"/>
     </row>
     <row r="1169">
       <c r="A1169" s="2" t="n">
@@ -12760,6 +13932,7 @@
       <c r="C1169" t="n">
         <v>0</v>
       </c>
+      <c r="D1169" t="inlineStr"/>
     </row>
     <row r="1170">
       <c r="A1170" s="2" t="n">
@@ -12769,6 +13942,7 @@
       <c r="C1170" t="n">
         <v>0</v>
       </c>
+      <c r="D1170" t="inlineStr"/>
     </row>
     <row r="1171">
       <c r="A1171" s="2" t="n">
@@ -12782,6 +13956,7 @@
       <c r="C1171" t="n">
         <v>1</v>
       </c>
+      <c r="D1171" t="inlineStr"/>
     </row>
     <row r="1172">
       <c r="A1172" s="2" t="n">
@@ -12795,6 +13970,7 @@
       <c r="C1172" t="n">
         <v>1</v>
       </c>
+      <c r="D1172" t="inlineStr"/>
     </row>
     <row r="1173">
       <c r="A1173" s="2" t="n">
@@ -12804,6 +13980,7 @@
       <c r="C1173" t="n">
         <v>0</v>
       </c>
+      <c r="D1173" t="inlineStr"/>
     </row>
     <row r="1174">
       <c r="A1174" s="2" t="n">
@@ -12813,6 +13990,7 @@
       <c r="C1174" t="n">
         <v>0</v>
       </c>
+      <c r="D1174" t="inlineStr"/>
     </row>
     <row r="1175">
       <c r="A1175" s="2" t="n">
@@ -12822,6 +14000,7 @@
       <c r="C1175" t="n">
         <v>0</v>
       </c>
+      <c r="D1175" t="inlineStr"/>
     </row>
     <row r="1176">
       <c r="A1176" s="2" t="n">
@@ -12831,6 +14010,7 @@
       <c r="C1176" t="n">
         <v>0</v>
       </c>
+      <c r="D1176" t="inlineStr"/>
     </row>
     <row r="1177">
       <c r="A1177" s="2" t="n">
@@ -12840,6 +14020,7 @@
       <c r="C1177" t="n">
         <v>0</v>
       </c>
+      <c r="D1177" t="inlineStr"/>
     </row>
     <row r="1178">
       <c r="A1178" s="2" t="n">
@@ -12853,6 +14034,7 @@
       <c r="C1178" t="n">
         <v>1</v>
       </c>
+      <c r="D1178" t="inlineStr"/>
     </row>
     <row r="1179">
       <c r="A1179" s="2" t="n">
@@ -12866,6 +14048,7 @@
       <c r="C1179" t="n">
         <v>1</v>
       </c>
+      <c r="D1179" t="inlineStr"/>
     </row>
     <row r="1180">
       <c r="A1180" s="2" t="n">
@@ -12875,6 +14058,7 @@
       <c r="C1180" t="n">
         <v>0</v>
       </c>
+      <c r="D1180" t="inlineStr"/>
     </row>
     <row r="1181">
       <c r="A1181" s="2" t="n">
@@ -12884,6 +14068,7 @@
       <c r="C1181" t="n">
         <v>0</v>
       </c>
+      <c r="D1181" t="inlineStr"/>
     </row>
     <row r="1182">
       <c r="A1182" s="2" t="n">
@@ -12893,6 +14078,7 @@
       <c r="C1182" t="n">
         <v>0</v>
       </c>
+      <c r="D1182" t="inlineStr"/>
     </row>
     <row r="1183">
       <c r="A1183" s="2" t="n">
@@ -12902,6 +14088,7 @@
       <c r="C1183" t="n">
         <v>0</v>
       </c>
+      <c r="D1183" t="inlineStr"/>
     </row>
     <row r="1184">
       <c r="A1184" s="2" t="n">
@@ -12911,6 +14098,7 @@
       <c r="C1184" t="n">
         <v>0</v>
       </c>
+      <c r="D1184" t="inlineStr"/>
     </row>
     <row r="1185">
       <c r="A1185" s="2" t="n">
@@ -12924,6 +14112,7 @@
       <c r="C1185" t="n">
         <v>1</v>
       </c>
+      <c r="D1185" t="inlineStr"/>
     </row>
     <row r="1186">
       <c r="A1186" s="2" t="n">
@@ -12937,6 +14126,7 @@
       <c r="C1186" t="n">
         <v>1</v>
       </c>
+      <c r="D1186" t="inlineStr"/>
     </row>
     <row r="1187">
       <c r="A1187" s="2" t="n">
@@ -12950,6 +14140,7 @@
       <c r="C1187" t="n">
         <v>1</v>
       </c>
+      <c r="D1187" t="inlineStr"/>
     </row>
     <row r="1188">
       <c r="A1188" s="2" t="n">
@@ -12963,6 +14154,7 @@
       <c r="C1188" t="n">
         <v>1</v>
       </c>
+      <c r="D1188" t="inlineStr"/>
     </row>
     <row r="1189">
       <c r="A1189" s="2" t="n">
@@ -12972,6 +14164,7 @@
       <c r="C1189" t="n">
         <v>0</v>
       </c>
+      <c r="D1189" t="inlineStr"/>
     </row>
     <row r="1190">
       <c r="A1190" s="2" t="n">
@@ -12981,6 +14174,7 @@
       <c r="C1190" t="n">
         <v>0</v>
       </c>
+      <c r="D1190" t="inlineStr"/>
     </row>
     <row r="1191">
       <c r="A1191" s="2" t="n">
@@ -12990,6 +14184,7 @@
       <c r="C1191" t="n">
         <v>0</v>
       </c>
+      <c r="D1191" t="inlineStr"/>
     </row>
     <row r="1192">
       <c r="A1192" s="2" t="n">
@@ -13003,6 +14198,7 @@
       <c r="C1192" t="n">
         <v>1</v>
       </c>
+      <c r="D1192" t="inlineStr"/>
     </row>
     <row r="1193">
       <c r="A1193" s="2" t="n">
@@ -13016,6 +14212,7 @@
       <c r="C1193" t="n">
         <v>1</v>
       </c>
+      <c r="D1193" t="inlineStr"/>
     </row>
     <row r="1194">
       <c r="A1194" s="2" t="n">
@@ -13025,6 +14222,7 @@
       <c r="C1194" t="n">
         <v>0</v>
       </c>
+      <c r="D1194" t="inlineStr"/>
     </row>
     <row r="1195">
       <c r="A1195" s="2" t="n">
@@ -13034,6 +14232,7 @@
       <c r="C1195" t="n">
         <v>0</v>
       </c>
+      <c r="D1195" t="inlineStr"/>
     </row>
     <row r="1196">
       <c r="A1196" s="2" t="n">
@@ -13043,6 +14242,7 @@
       <c r="C1196" t="n">
         <v>0</v>
       </c>
+      <c r="D1196" t="inlineStr"/>
     </row>
     <row r="1197">
       <c r="A1197" s="2" t="n">
@@ -13052,6 +14252,7 @@
       <c r="C1197" t="n">
         <v>0</v>
       </c>
+      <c r="D1197" t="inlineStr"/>
     </row>
     <row r="1198">
       <c r="A1198" s="2" t="n">
@@ -13061,6 +14262,7 @@
       <c r="C1198" t="n">
         <v>0</v>
       </c>
+      <c r="D1198" t="inlineStr"/>
     </row>
     <row r="1199">
       <c r="A1199" s="2" t="n">
@@ -13074,6 +14276,7 @@
       <c r="C1199" t="n">
         <v>1</v>
       </c>
+      <c r="D1199" t="inlineStr"/>
     </row>
     <row r="1200">
       <c r="A1200" s="2" t="n">
@@ -13087,6 +14290,7 @@
       <c r="C1200" t="n">
         <v>1</v>
       </c>
+      <c r="D1200" t="inlineStr"/>
     </row>
     <row r="1201">
       <c r="A1201" s="2" t="n">
@@ -13096,6 +14300,7 @@
       <c r="C1201" t="n">
         <v>0</v>
       </c>
+      <c r="D1201" t="inlineStr"/>
     </row>
     <row r="1202">
       <c r="A1202" s="2" t="n">
@@ -13105,6 +14310,7 @@
       <c r="C1202" t="n">
         <v>0</v>
       </c>
+      <c r="D1202" t="inlineStr"/>
     </row>
     <row r="1203">
       <c r="A1203" s="2" t="n">
@@ -13114,6 +14320,7 @@
       <c r="C1203" t="n">
         <v>0</v>
       </c>
+      <c r="D1203" t="inlineStr"/>
     </row>
     <row r="1204">
       <c r="A1204" s="2" t="n">
@@ -13123,6 +14330,7 @@
       <c r="C1204" t="n">
         <v>0</v>
       </c>
+      <c r="D1204" t="inlineStr"/>
     </row>
     <row r="1205">
       <c r="A1205" s="2" t="n">
@@ -13136,6 +14344,7 @@
       <c r="C1205" t="n">
         <v>1</v>
       </c>
+      <c r="D1205" t="inlineStr"/>
     </row>
     <row r="1206">
       <c r="A1206" s="2" t="n">
@@ -13149,6 +14358,7 @@
       <c r="C1206" t="n">
         <v>1</v>
       </c>
+      <c r="D1206" t="inlineStr"/>
     </row>
     <row r="1207">
       <c r="A1207" s="2" t="n">
@@ -13162,6 +14372,7 @@
       <c r="C1207" t="n">
         <v>1</v>
       </c>
+      <c r="D1207" t="inlineStr"/>
     </row>
     <row r="1208">
       <c r="A1208" s="2" t="n">
@@ -13171,6 +14382,7 @@
       <c r="C1208" t="n">
         <v>0</v>
       </c>
+      <c r="D1208" t="inlineStr"/>
     </row>
     <row r="1209">
       <c r="A1209" s="2" t="n">
@@ -13180,6 +14392,7 @@
       <c r="C1209" t="n">
         <v>0</v>
       </c>
+      <c r="D1209" t="inlineStr"/>
     </row>
     <row r="1210">
       <c r="A1210" s="2" t="n">
@@ -13189,6 +14402,7 @@
       <c r="C1210" t="n">
         <v>0</v>
       </c>
+      <c r="D1210" t="inlineStr"/>
     </row>
     <row r="1211">
       <c r="A1211" s="2" t="n">
@@ -13198,6 +14412,7 @@
       <c r="C1211" t="n">
         <v>0</v>
       </c>
+      <c r="D1211" t="inlineStr"/>
     </row>
     <row r="1212">
       <c r="A1212" s="2" t="n">
@@ -13207,6 +14422,7 @@
       <c r="C1212" t="n">
         <v>0</v>
       </c>
+      <c r="D1212" t="inlineStr"/>
     </row>
     <row r="1213">
       <c r="A1213" s="2" t="n">
@@ -13220,6 +14436,7 @@
       <c r="C1213" t="n">
         <v>1</v>
       </c>
+      <c r="D1213" t="inlineStr"/>
     </row>
     <row r="1214">
       <c r="A1214" s="2" t="n">
@@ -13233,6 +14450,7 @@
       <c r="C1214" t="n">
         <v>1</v>
       </c>
+      <c r="D1214" t="inlineStr"/>
     </row>
     <row r="1215">
       <c r="A1215" s="2" t="n">
@@ -13242,6 +14460,7 @@
       <c r="C1215" t="n">
         <v>0</v>
       </c>
+      <c r="D1215" t="inlineStr"/>
     </row>
     <row r="1216">
       <c r="A1216" s="2" t="n">
@@ -13251,6 +14470,7 @@
       <c r="C1216" t="n">
         <v>0</v>
       </c>
+      <c r="D1216" t="inlineStr"/>
     </row>
     <row r="1217">
       <c r="A1217" s="2" t="n">
@@ -13260,6 +14480,7 @@
       <c r="C1217" t="n">
         <v>0</v>
       </c>
+      <c r="D1217" t="inlineStr"/>
     </row>
     <row r="1218">
       <c r="A1218" s="2" t="n">
@@ -13273,6 +14494,7 @@
       <c r="C1218" t="n">
         <v>1</v>
       </c>
+      <c r="D1218" t="inlineStr"/>
     </row>
     <row r="1219">
       <c r="A1219" s="2" t="n">
@@ -13282,6 +14504,7 @@
       <c r="C1219" t="n">
         <v>0</v>
       </c>
+      <c r="D1219" t="inlineStr"/>
     </row>
     <row r="1220">
       <c r="A1220" s="2" t="n">
@@ -13295,6 +14518,7 @@
       <c r="C1220" t="n">
         <v>1</v>
       </c>
+      <c r="D1220" t="inlineStr"/>
     </row>
     <row r="1221">
       <c r="A1221" s="2" t="n">
@@ -13308,6 +14532,7 @@
       <c r="C1221" t="n">
         <v>1</v>
       </c>
+      <c r="D1221" t="inlineStr"/>
     </row>
     <row r="1222">
       <c r="A1222" s="2" t="n">
@@ -13315,6 +14540,39 @@
       </c>
       <c r="B1222" t="inlineStr"/>
       <c r="C1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1222" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="B1223" t="inlineStr"/>
+      <c r="C1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2" t="n">
+        <v>45784</v>
+      </c>
+      <c r="B1224" t="inlineStr"/>
+      <c r="C1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="2" t="n">
+        <v>45785</v>
+      </c>
+      <c r="B1225" t="inlineStr"/>
+      <c r="C1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1225" t="n">
         <v>0</v>
       </c>
     </row>

--- a/files/holidays_ID.xlsx
+++ b/files/holidays_ID.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1225"/>
+  <dimension ref="A1:D1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14576,6 +14576,140 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="B1226" t="inlineStr"/>
+      <c r="C1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1226" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1227" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="n">
+        <v>45788</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1228" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="n">
+        <v>45789</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Hari Raya Waisak</t>
+        </is>
+      </c>
+      <c r="C1229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1229" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="n">
+        <v>45790</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Cuti Waisak</t>
+        </is>
+      </c>
+      <c r="C1230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="B1231" t="inlineStr"/>
+      <c r="C1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1231" t="inlineStr"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B1232" t="inlineStr"/>
+      <c r="C1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1232" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="2" t="n">
+        <v>45793</v>
+      </c>
+      <c r="B1233" t="inlineStr"/>
+      <c r="C1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1233" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="2" t="n">
+        <v>45794</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1234" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="2" t="n">
+        <v>45795</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1235" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="B1236" t="inlineStr"/>
+      <c r="C1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1236" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/holidays_ID.xlsx
+++ b/files/holidays_ID.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1236"/>
+  <dimension ref="A1:D1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14710,6 +14710,356 @@
       </c>
       <c r="D1236" t="inlineStr"/>
     </row>
+    <row r="1237">
+      <c r="A1237" s="2" t="n">
+        <v>45797</v>
+      </c>
+      <c r="B1237" t="inlineStr"/>
+      <c r="C1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1237" t="inlineStr"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2" t="n">
+        <v>45798</v>
+      </c>
+      <c r="B1238" t="inlineStr"/>
+      <c r="C1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1238" t="inlineStr"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="2" t="n">
+        <v>45799</v>
+      </c>
+      <c r="B1239" t="inlineStr"/>
+      <c r="C1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1239" t="inlineStr"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="B1240" t="inlineStr"/>
+      <c r="C1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1240" t="inlineStr"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2" t="n">
+        <v>45801</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1241" t="inlineStr"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2" t="n">
+        <v>45802</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1242" t="inlineStr"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="2" t="n">
+        <v>45803</v>
+      </c>
+      <c r="B1243" t="inlineStr"/>
+      <c r="C1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1243" t="inlineStr"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2" t="n">
+        <v>45804</v>
+      </c>
+      <c r="B1244" t="inlineStr"/>
+      <c r="C1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1244" t="inlineStr"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="2" t="n">
+        <v>45805</v>
+      </c>
+      <c r="B1245" t="inlineStr"/>
+      <c r="C1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1245" t="inlineStr"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2" t="n">
+        <v>45806</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Kenaikan Yesus Kristus</t>
+        </is>
+      </c>
+      <c r="C1246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1246" t="inlineStr"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="2" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B1247" t="inlineStr"/>
+      <c r="C1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1247" t="inlineStr"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1248" t="inlineStr"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="2" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Hari Lahir Pancasila</t>
+        </is>
+      </c>
+      <c r="C1249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1249" t="inlineStr"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B1250" t="inlineStr"/>
+      <c r="C1250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1250" t="inlineStr"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="B1251" t="inlineStr"/>
+      <c r="C1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1251" t="inlineStr"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="B1252" t="inlineStr"/>
+      <c r="C1252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1252" t="inlineStr"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="2" t="n">
+        <v>45813</v>
+      </c>
+      <c r="B1253" t="inlineStr"/>
+      <c r="C1253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1253" t="inlineStr"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Hari Raya Idul Adha</t>
+        </is>
+      </c>
+      <c r="C1254" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1254" t="inlineStr"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="2" t="n">
+        <v>45815</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1255" t="inlineStr"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2" t="n">
+        <v>45816</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1256" t="inlineStr"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="2" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B1257" t="inlineStr"/>
+      <c r="C1257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1257" t="inlineStr"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2" t="n">
+        <v>45818</v>
+      </c>
+      <c r="B1258" t="inlineStr"/>
+      <c r="C1258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1258" t="inlineStr"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="2" t="n">
+        <v>45819</v>
+      </c>
+      <c r="B1259" t="inlineStr"/>
+      <c r="C1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1259" t="inlineStr"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2" t="n">
+        <v>45820</v>
+      </c>
+      <c r="B1260" t="inlineStr"/>
+      <c r="C1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1260" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="2" t="n">
+        <v>45821</v>
+      </c>
+      <c r="B1261" t="inlineStr"/>
+      <c r="C1261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1261" t="inlineStr"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="2" t="n">
+        <v>45822</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1262" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1262" t="inlineStr"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="2" t="n">
+        <v>45823</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Weekend</t>
+        </is>
+      </c>
+      <c r="C1263" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1263" t="inlineStr"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="B1264" t="inlineStr"/>
+      <c r="C1264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1264" t="inlineStr"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="2" t="n">
+        <v>45825</v>
+      </c>
+      <c r="B1265" t="inlineStr"/>
+      <c r="C1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1265" t="inlineStr"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B1266" t="inlineStr"/>
+      <c r="C1266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1266" t="inlineStr"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2" t="n">
+        <v>45827</v>
+      </c>
+      <c r="B1267" t="inlineStr"/>
+      <c r="C1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1267" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
